--- a/data/finAlign/File1/RPT_RPT9892372453518NR_finAlign.xlsx
+++ b/data/finAlign/File1/RPT_RPT9892372453518NR_finAlign.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FinAlign" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FinAlign" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2309,16 +2309,16 @@
         <v>51776.79157354531</v>
       </c>
       <c r="CL5" t="n">
-        <v>43354.81400037728</v>
+        <v>43354.81400037729</v>
       </c>
       <c r="CN5" t="n">
         <v>24105.92564488243</v>
       </c>
       <c r="CO5" t="n">
-        <v>43354.81400037728</v>
+        <v>43354.81400037729</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.5560149709020239</v>
+        <v>0.5560149709020238</v>
       </c>
       <c r="CR5" t="n">
         <v>21894.18107019053</v>
@@ -2357,7 +2357,7 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.5560149709020239</v>
+        <v>0.5560149709020238</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -2486,13 +2486,13 @@
         <v>64035.71048123318</v>
       </c>
       <c r="FB5" t="n">
-        <v>37514.37281980563</v>
+        <v>37514.37281980564</v>
       </c>
       <c r="FC5" t="n">
         <v>64035.71048123318</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.5858351931739697</v>
+        <v>0.5858351931739698</v>
       </c>
       <c r="FF5" t="n">
         <v>32338.03379302276</v>
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>37514.37281980563</v>
+        <v>37514.37281980564</v>
       </c>
       <c r="FP5" t="n">
         <v>0</v>
@@ -2531,7 +2531,7 @@
         <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.5858351931739697</v>
+        <v>0.5858351931739698</v>
       </c>
       <c r="FT5" t="n">
         <v>0</v>
@@ -2805,10 +2805,10 @@
         <v>18064.50583349054</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.5560149709020239</v>
+        <v>0.5560149709020238</v>
       </c>
       <c r="CR6" t="n">
-        <v>9122.575445912722</v>
+        <v>9122.575445912724</v>
       </c>
       <c r="CS6" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.5560149709020239</v>
+        <v>0.5560149709020238</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>26681.54603384716</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.5858351931739697</v>
+        <v>0.5858351931739698</v>
       </c>
       <c r="FF6" t="n">
         <v>13474.18074709282</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.5858351931739697</v>
+        <v>0.5858351931739698</v>
       </c>
       <c r="FT6" t="n">
         <v>0</v>
@@ -3283,19 +3283,19 @@
         <v>25888.39578677265</v>
       </c>
       <c r="CL7" t="n">
-        <v>21677.40700018864</v>
+        <v>21677.40700018865</v>
       </c>
       <c r="CN7" t="n">
         <v>12052.96282244122</v>
       </c>
       <c r="CO7" t="n">
-        <v>21677.40700018864</v>
+        <v>21677.40700018865</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.5560149709020239</v>
+        <v>0.5560149709020238</v>
       </c>
       <c r="CR7" t="n">
-        <v>10947.09053509526</v>
+        <v>10947.09053509527</v>
       </c>
       <c r="CS7" t="n">
         <v>0</v>
@@ -3331,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.5560149709020239</v>
+        <v>0.5560149709020238</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -3466,7 +3466,7 @@
         <v>32017.85524061659</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.5858351931739697</v>
+        <v>0.5858351931739698</v>
       </c>
       <c r="FF7" t="n">
         <v>16169.01689651138</v>
@@ -3505,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.5858351931739697</v>
+        <v>0.5858351931739698</v>
       </c>
       <c r="FT7" t="n">
         <v>0</v>
@@ -3578,7 +3578,7 @@
         <v>0.01057447839568068</v>
       </c>
       <c r="R8" t="n">
-        <v>25759.6847762122</v>
+        <v>25759.68477621219</v>
       </c>
       <c r="S8" t="n">
         <v>21569.63203474447</v>
@@ -3767,19 +3767,19 @@
         <v>9.835629504558808</v>
       </c>
       <c r="CK8" t="n">
-        <v>39471.18585030855</v>
+        <v>39471.18585030856</v>
       </c>
       <c r="CL8" t="n">
-        <v>33050.82970395563</v>
+        <v>33050.82970395564</v>
       </c>
       <c r="CN8" t="n">
         <v>18376.75611613264</v>
       </c>
       <c r="CO8" t="n">
-        <v>33050.82970395563</v>
+        <v>33050.82970395564</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.5560149709020239</v>
+        <v>0.5560149709020238</v>
       </c>
       <c r="CR8" t="n">
         <v>16690.6690004976</v>
@@ -3818,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.5560149709020239</v>
+        <v>0.5560149709020238</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -3857,19 +3857,19 @@
         <v>47810.70521344606</v>
       </c>
       <c r="DS8" t="n">
-        <v>40033.84854025807</v>
+        <v>40033.84854025806</v>
       </c>
       <c r="DU8" t="n">
         <v>22869.27497971527</v>
       </c>
       <c r="DV8" t="n">
-        <v>40033.84854025807</v>
+        <v>40033.84854025806</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.5712484763166825</v>
+        <v>0.5712484763166827</v>
       </c>
       <c r="DY8" t="n">
-        <v>20217.09351283032</v>
+        <v>20217.09351283033</v>
       </c>
       <c r="DZ8" t="n">
         <v>0</v>
@@ -3881,7 +3881,7 @@
         <v>0</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.505</v>
+        <v>0.5050000000000001</v>
       </c>
       <c r="ED8" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
         <v>0</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.5712484763166825</v>
+        <v>0.5712484763166827</v>
       </c>
       <c r="EM8" t="n">
         <v>0</v>
@@ -3929,7 +3929,7 @@
         <v>57730.75952551893</v>
       </c>
       <c r="EU8" t="n">
-        <v>48340.3135896163</v>
+        <v>48340.31358961629</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -3947,13 +3947,13 @@
         <v>48341.82203571145</v>
       </c>
       <c r="FB8" t="n">
-        <v>28320.34065067268</v>
+        <v>28320.34065067269</v>
       </c>
       <c r="FC8" t="n">
         <v>48341.82203571145</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.5858351931739697</v>
+        <v>0.5858351931739698</v>
       </c>
       <c r="FF8" t="n">
         <v>24412.62012803428</v>
@@ -3980,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>28320.34065067268</v>
+        <v>28320.34065067269</v>
       </c>
       <c r="FP8" t="n">
         <v>0</v>
@@ -3992,7 +3992,7 @@
         <v>0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.5858351931739697</v>
+        <v>0.5858351931739698</v>
       </c>
       <c r="FT8" t="n">
         <v>0</v>
@@ -4254,22 +4254,22 @@
         <v>6.451001254224708</v>
       </c>
       <c r="CK9" t="n">
-        <v>8629.465262257552</v>
+        <v>8629.465262257554</v>
       </c>
       <c r="CL9" t="n">
-        <v>7225.802333396215</v>
+        <v>7225.802333396216</v>
       </c>
       <c r="CN9" t="n">
         <v>4017.654274147072</v>
       </c>
       <c r="CO9" t="n">
-        <v>7225.802333396215</v>
+        <v>7225.802333396216</v>
       </c>
       <c r="CP9" t="n">
         <v>0.5560149709020238</v>
       </c>
       <c r="CR9" t="n">
-        <v>3649.030178365088</v>
+        <v>3649.030178365089</v>
       </c>
       <c r="CS9" t="n">
         <v>0</v>
@@ -4434,13 +4434,13 @@
         <v>10672.61841353886</v>
       </c>
       <c r="FB9" t="n">
-        <v>6252.395469967605</v>
+        <v>6252.395469967607</v>
       </c>
       <c r="FC9" t="n">
         <v>10672.61841353886</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.5858351931739696</v>
+        <v>0.5858351931739698</v>
       </c>
       <c r="FF9" t="n">
         <v>5389.672298837126</v>
@@ -4467,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="FO9" t="n">
-        <v>6252.395469967605</v>
+        <v>6252.395469967607</v>
       </c>
       <c r="FP9" t="n">
         <v>0</v>
@@ -4479,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.5858351931739696</v>
+        <v>0.5858351931739698</v>
       </c>
       <c r="FT9" t="n">
         <v>0</v>
@@ -4741,16 +4741,16 @@
         <v>6.725678639324976</v>
       </c>
       <c r="CK10" t="n">
-        <v>28470.85819159409</v>
+        <v>28470.8581915941</v>
       </c>
       <c r="CL10" t="n">
-        <v>23725.71515966174</v>
+        <v>23725.71515966175</v>
       </c>
       <c r="CN10" t="n">
         <v>0</v>
       </c>
       <c r="CO10" t="n">
-        <v>23725.71515966174</v>
+        <v>23725.71515966175</v>
       </c>
       <c r="CP10" t="n">
         <v>0</v>
@@ -5228,16 +5228,16 @@
         <v>10.08851795898746</v>
       </c>
       <c r="CK11" t="n">
-        <v>42706.28728739114</v>
+        <v>42706.28728739115</v>
       </c>
       <c r="CL11" t="n">
-        <v>35588.57273949261</v>
+        <v>35588.57273949262</v>
       </c>
       <c r="CN11" t="n">
         <v>0</v>
       </c>
       <c r="CO11" t="n">
-        <v>35588.57273949261</v>
+        <v>35588.57273949262</v>
       </c>
       <c r="CP11" t="n">
         <v>0</v>
@@ -5715,7 +5715,7 @@
         <v>3.362839319662488</v>
       </c>
       <c r="CK12" t="n">
-        <v>14235.42909579704</v>
+        <v>14235.42909579705</v>
       </c>
       <c r="CL12" t="n">
         <v>11862.85757983087</v>
@@ -6202,16 +6202,16 @@
         <v>3.362839319662488</v>
       </c>
       <c r="CK13" t="n">
-        <v>9490.286063864698</v>
+        <v>9490.2860638647</v>
       </c>
       <c r="CL13" t="n">
-        <v>7908.571719887248</v>
+        <v>7908.57171988725</v>
       </c>
       <c r="CN13" t="n">
         <v>0</v>
       </c>
       <c r="CO13" t="n">
-        <v>7908.571719887248</v>
+        <v>7908.57171988725</v>
       </c>
       <c r="CP13" t="n">
         <v>0</v>
@@ -6680,7 +6680,7 @@
         <v>829.7329234160946</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.009476114063963091</v>
+        <v>0.009476114063963093</v>
       </c>
       <c r="CI14" t="n">
         <v>0</v>
@@ -6689,22 +6689,22 @@
         <v>4.155849806699564</v>
       </c>
       <c r="CK14" t="n">
-        <v>4107.07457611452</v>
+        <v>4107.074576114521</v>
       </c>
       <c r="CL14" t="n">
-        <v>827.2956918274605</v>
+        <v>827.2956918274607</v>
       </c>
       <c r="CN14" t="n">
         <v>81.978200201373</v>
       </c>
       <c r="CO14" t="n">
-        <v>827.2956918274605</v>
+        <v>827.2956918274607</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0990917769924399</v>
+        <v>0.09909177699243987</v>
       </c>
       <c r="CR14" t="n">
-        <v>74.45661226447145</v>
+        <v>74.45661226447146</v>
       </c>
       <c r="CS14" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
         <v>0</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.0990917769924399</v>
+        <v>0.09909177699243987</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -6854,7 +6854,7 @@
         <v>757.6788753161321</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.008635392449455182</v>
+        <v>0.008635392449455184</v>
       </c>
       <c r="EW14" t="n">
         <v>0</v>
@@ -6869,7 +6869,7 @@
         <v>755.9822946221916</v>
       </c>
       <c r="FB14" t="n">
-        <v>78.92929311791747</v>
+        <v>78.92929311791748</v>
       </c>
       <c r="FC14" t="n">
         <v>755.9822946221916</v>
@@ -6902,7 +6902,7 @@
         <v>0</v>
       </c>
       <c r="FO14" t="n">
-        <v>78.92929311791747</v>
+        <v>78.92929311791748</v>
       </c>
       <c r="FP14" t="n">
         <v>0</v>
@@ -7468,7 +7468,7 @@
         <v>8660.650673699445</v>
       </c>
       <c r="P16" t="n">
-        <v>87.98185527929141</v>
+        <v>87.98185527929142</v>
       </c>
       <c r="Q16" t="n">
         <v>0.1421792000668838</v>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>87.98185527929141</v>
+        <v>87.98185527929142</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -7672,7 +7672,7 @@
         <v>0</v>
       </c>
       <c r="CO16" t="n">
-        <v>8123.910148932865</v>
+        <v>8123.910148932867</v>
       </c>
       <c r="CP16" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>425.1296198658507</v>
+        <v>425.1296198658506</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -8072,7 +8072,7 @@
         <v>0</v>
       </c>
       <c r="BH17" t="n">
-        <v>148.0119495662651</v>
+        <v>148.011949566265</v>
       </c>
       <c r="BI17" t="n">
         <v>0</v>
@@ -9611,16 +9611,16 @@
         <v>2.991723673149686</v>
       </c>
       <c r="CK20" t="n">
-        <v>4800.056420497155</v>
+        <v>4800.056420497156</v>
       </c>
       <c r="CL20" t="n">
-        <v>4000.047017080963</v>
+        <v>4000.047017080964</v>
       </c>
       <c r="CN20" t="n">
         <v>0</v>
       </c>
       <c r="CO20" t="n">
-        <v>4000.047017080963</v>
+        <v>4000.047017080964</v>
       </c>
       <c r="CP20" t="n">
         <v>0</v>
@@ -10098,16 +10098,16 @@
         <v>4.080586379324645</v>
       </c>
       <c r="CK21" t="n">
-        <v>3838.667851558415</v>
+        <v>3838.667851558416</v>
       </c>
       <c r="CL21" t="n">
-        <v>3198.889876298679</v>
+        <v>3198.88987629868</v>
       </c>
       <c r="CN21" t="n">
         <v>0</v>
       </c>
       <c r="CO21" t="n">
-        <v>3198.889876298679</v>
+        <v>3198.88987629868</v>
       </c>
       <c r="CP21" t="n">
         <v>0</v>
@@ -11072,16 +11072,16 @@
         <v>5.302578433760297</v>
       </c>
       <c r="CK23" t="n">
-        <v>4386.369994415018</v>
+        <v>4386.36999441502</v>
       </c>
       <c r="CL23" t="n">
-        <v>3655.308328679183</v>
+        <v>3655.308328679184</v>
       </c>
       <c r="CN23" t="n">
         <v>0</v>
       </c>
       <c r="CO23" t="n">
-        <v>3655.308328679183</v>
+        <v>3655.308328679184</v>
       </c>
       <c r="CP23" t="n">
         <v>0</v>
@@ -11376,7 +11376,7 @@
         <v>847.5532125756087</v>
       </c>
       <c r="T24" t="n">
-        <v>0.004173738291715312</v>
+        <v>0.004173738291715311</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -11550,7 +11550,7 @@
         <v>833.6571509388259</v>
       </c>
       <c r="CH24" t="n">
-        <v>0.003790445625585237</v>
+        <v>0.003790445625585238</v>
       </c>
       <c r="CI24" t="n">
         <v>0</v>
@@ -11559,22 +11559,22 @@
         <v>1.662339922679826</v>
       </c>
       <c r="CK24" t="n">
-        <v>972.5784334287634</v>
+        <v>972.5784334287637</v>
       </c>
       <c r="CL24" t="n">
-        <v>831.2083924467636</v>
+        <v>831.2083924467638</v>
       </c>
       <c r="CN24" t="n">
         <v>594.8649536452939</v>
       </c>
       <c r="CO24" t="n">
-        <v>831.2083924467636</v>
+        <v>831.2083924467638</v>
       </c>
       <c r="CP24" t="n">
-        <v>0.7156628338342881</v>
+        <v>0.7156628338342879</v>
       </c>
       <c r="CR24" t="n">
-        <v>540.2854550903963</v>
+        <v>540.2854550903965</v>
       </c>
       <c r="CS24" t="n">
         <v>0</v>
@@ -11610,7 +11610,7 @@
         <v>0</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.7156628338342881</v>
+        <v>0.7156628338342879</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -11724,7 +11724,7 @@
         <v>803.7293567745004</v>
       </c>
       <c r="EV24" t="n">
-        <v>0.003454156979782073</v>
+        <v>0.003454156979782074</v>
       </c>
       <c r="EW24" t="n">
         <v>0</v>
@@ -11739,13 +11739,13 @@
         <v>801.9296606838737</v>
       </c>
       <c r="FB24" t="n">
-        <v>604.6912900814605</v>
+        <v>604.6912900814606</v>
       </c>
       <c r="FC24" t="n">
         <v>801.9296606838737</v>
       </c>
       <c r="FD24" t="n">
-        <v>0.7540452981447134</v>
+        <v>0.7540452981447135</v>
       </c>
       <c r="FF24" t="n">
         <v>521.2542794445179</v>
@@ -11772,7 +11772,7 @@
         <v>0</v>
       </c>
       <c r="FO24" t="n">
-        <v>604.6912900814605</v>
+        <v>604.6912900814606</v>
       </c>
       <c r="FP24" t="n">
         <v>0</v>
@@ -11784,7 +11784,7 @@
         <v>0</v>
       </c>
       <c r="FS24" t="n">
-        <v>0.7540452981447134</v>
+        <v>0.7540452981447135</v>
       </c>
       <c r="FT24" t="n">
         <v>0</v>
@@ -12049,13 +12049,13 @@
         <v>1290.976487067273</v>
       </c>
       <c r="CL25" t="n">
-        <v>1075.813739222727</v>
+        <v>1075.813739222728</v>
       </c>
       <c r="CN25" t="n">
         <v>0</v>
       </c>
       <c r="CO25" t="n">
-        <v>1075.813739222727</v>
+        <v>1075.813739222728</v>
       </c>
       <c r="CP25" t="n">
         <v>0</v>
@@ -12533,19 +12533,19 @@
         <v>1.138136624931009</v>
       </c>
       <c r="CK26" t="n">
-        <v>5824.238793755201</v>
+        <v>5824.238793755202</v>
       </c>
       <c r="CL26" t="n">
-        <v>4923.176076048352</v>
+        <v>4923.176076048353</v>
       </c>
       <c r="CN26" t="n">
         <v>1951.385063289194</v>
       </c>
       <c r="CO26" t="n">
-        <v>4923.176076048352</v>
+        <v>4923.176076048353</v>
       </c>
       <c r="CP26" t="n">
-        <v>0.3963671079697596</v>
+        <v>0.3963671079697594</v>
       </c>
       <c r="CR26" t="n">
         <v>1772.343387377407</v>
@@ -12584,7 +12584,7 @@
         <v>0</v>
       </c>
       <c r="DE26" t="n">
-        <v>0.3963671079697596</v>
+        <v>0.3963671079697594</v>
       </c>
       <c r="DF26" t="n">
         <v>0</v>
@@ -12713,13 +12713,13 @@
         <v>5548.417078355887</v>
       </c>
       <c r="FB26" t="n">
-        <v>2317.158171736662</v>
+        <v>2317.158171736663</v>
       </c>
       <c r="FC26" t="n">
         <v>5548.417078355887</v>
       </c>
       <c r="FD26" t="n">
-        <v>0.4176250882032259</v>
+        <v>0.417625088203226</v>
       </c>
       <c r="FF26" t="n">
         <v>1997.430148208119</v>
@@ -12746,7 +12746,7 @@
         <v>0</v>
       </c>
       <c r="FO26" t="n">
-        <v>2317.158171736662</v>
+        <v>2317.158171736663</v>
       </c>
       <c r="FP26" t="n">
         <v>0</v>
@@ -12758,7 +12758,7 @@
         <v>0</v>
       </c>
       <c r="FS26" t="n">
-        <v>0.4176250882032259</v>
+        <v>0.417625088203226</v>
       </c>
       <c r="FT26" t="n">
         <v>0</v>
@@ -13032,7 +13032,7 @@
         <v>3121.18237038505</v>
       </c>
       <c r="CP27" t="n">
-        <v>0.4068267955411838</v>
+        <v>0.4068267955411836</v>
       </c>
       <c r="CR27" t="n">
         <v>1153.276885857276</v>
@@ -13071,7 +13071,7 @@
         <v>0</v>
       </c>
       <c r="DE27" t="n">
-        <v>0.4068267955411838</v>
+        <v>0.4068267955411836</v>
       </c>
       <c r="DF27" t="n">
         <v>0</v>
@@ -13200,13 +13200,13 @@
         <v>3916.089188613881</v>
       </c>
       <c r="FB27" t="n">
-        <v>1678.614988311189</v>
+        <v>1678.61498831119</v>
       </c>
       <c r="FC27" t="n">
         <v>3916.089188613881</v>
       </c>
       <c r="FD27" t="n">
-        <v>0.4286457502530333</v>
+        <v>0.4286457502530334</v>
       </c>
       <c r="FF27" t="n">
         <v>1446.994955192829</v>
@@ -13233,7 +13233,7 @@
         <v>0</v>
       </c>
       <c r="FO27" t="n">
-        <v>1678.614988311189</v>
+        <v>1678.61498831119</v>
       </c>
       <c r="FP27" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>0</v>
       </c>
       <c r="FS27" t="n">
-        <v>0.4286457502530333</v>
+        <v>0.4286457502530334</v>
       </c>
       <c r="FT27" t="n">
         <v>0</v>
@@ -13507,7 +13507,7 @@
         <v>0.01494469002055955</v>
       </c>
       <c r="CK28" t="n">
-        <v>13.18699690319039</v>
+        <v>13.1869969031904</v>
       </c>
       <c r="CL28" t="n">
         <v>10.989164085992</v>
@@ -13994,7 +13994,7 @@
         <v>0.9972412243832286</v>
       </c>
       <c r="CK29" t="n">
-        <v>397.3949446767251</v>
+        <v>397.3949446767252</v>
       </c>
       <c r="CL29" t="n">
         <v>331.162453897271</v>
@@ -14316,7 +14316,7 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>84693.89027436396</v>
+        <v>84693.89027436393</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -14403,7 +14403,7 @@
         <v>0</v>
       </c>
       <c r="BH30" t="n">
-        <v>56147.23036396676</v>
+        <v>56147.23036396674</v>
       </c>
       <c r="BI30" t="n">
         <v>0</v>
@@ -14490,7 +14490,7 @@
         <v>0</v>
       </c>
       <c r="CO30" t="n">
-        <v>57324.5306300817</v>
+        <v>57324.53063008167</v>
       </c>
       <c r="CP30" t="n">
         <v>0</v>
@@ -14577,7 +14577,7 @@
         <v>0</v>
       </c>
       <c r="DV30" t="n">
-        <v>61269.40136856282</v>
+        <v>61269.4013685628</v>
       </c>
       <c r="DW30" t="n">
         <v>0</v>
@@ -14968,16 +14968,16 @@
         <v>0.9972412243832286</v>
       </c>
       <c r="CK31" t="n">
-        <v>445.9699596735598</v>
+        <v>445.9699596735599</v>
       </c>
       <c r="CL31" t="n">
-        <v>371.6416330612998</v>
+        <v>371.6416330613</v>
       </c>
       <c r="CN31" t="n">
         <v>0</v>
       </c>
       <c r="CO31" t="n">
-        <v>371.6416330612998</v>
+        <v>371.6416330613</v>
       </c>
       <c r="CP31" t="n">
         <v>0</v>
@@ -15455,16 +15455,16 @@
         <v>5.889508681051359</v>
       </c>
       <c r="CK32" t="n">
-        <v>7193.611798589584</v>
+        <v>7193.611798589586</v>
       </c>
       <c r="CL32" t="n">
-        <v>5994.676498824654</v>
+        <v>5994.676498824655</v>
       </c>
       <c r="CN32" t="n">
         <v>0</v>
       </c>
       <c r="CO32" t="n">
-        <v>5994.676498824654</v>
+        <v>5994.676498824655</v>
       </c>
       <c r="CP32" t="n">
         <v>0</v>
@@ -15942,13 +15942,13 @@
         <v>1.994482448766457</v>
       </c>
       <c r="CK33" t="n">
-        <v>3875.852608296994</v>
+        <v>3875.852608296995</v>
       </c>
       <c r="CL33" t="n">
         <v>3273.286623959782</v>
       </c>
       <c r="CN33" t="n">
-        <v>900.9883004826643</v>
+        <v>900.9883004826642</v>
       </c>
       <c r="CO33" t="n">
         <v>3273.286623959782</v>
@@ -15957,7 +15957,7 @@
         <v>0.2752549360901108</v>
       </c>
       <c r="CR33" t="n">
-        <v>818.3216559899454</v>
+        <v>818.3216559899455</v>
       </c>
       <c r="CS33" t="n">
         <v>0</v>
@@ -15981,7 +15981,7 @@
         <v>0</v>
       </c>
       <c r="DA33" t="n">
-        <v>900.9883004826643</v>
+        <v>900.9883004826642</v>
       </c>
       <c r="DB33" t="n">
         <v>0</v>
@@ -16122,13 +16122,13 @@
         <v>3379.27547739771</v>
       </c>
       <c r="FB33" t="n">
-        <v>980.0487634105674</v>
+        <v>980.0487634105676</v>
       </c>
       <c r="FC33" t="n">
         <v>3379.27547739771</v>
       </c>
       <c r="FD33" t="n">
-        <v>0.2900174223633513</v>
+        <v>0.2900174223633514</v>
       </c>
       <c r="FF33" t="n">
         <v>844.8188693494276</v>
@@ -16155,7 +16155,7 @@
         <v>0</v>
       </c>
       <c r="FO33" t="n">
-        <v>980.0487634105674</v>
+        <v>980.0487634105676</v>
       </c>
       <c r="FP33" t="n">
         <v>0</v>
@@ -16167,7 +16167,7 @@
         <v>0</v>
       </c>
       <c r="FS33" t="n">
-        <v>0.2900174223633513</v>
+        <v>0.2900174223633514</v>
       </c>
       <c r="FT33" t="n">
         <v>0</v>
@@ -16429,16 +16429,16 @@
         <v>1.0300214586463</v>
       </c>
       <c r="CK34" t="n">
-        <v>821.7968280269948</v>
+        <v>821.7968280269951</v>
       </c>
       <c r="CL34" t="n">
-        <v>684.8306900224958</v>
+        <v>684.8306900224959</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
       </c>
       <c r="CO34" t="n">
-        <v>684.8306900224958</v>
+        <v>684.8306900224959</v>
       </c>
       <c r="CP34" t="n">
         <v>0</v>
@@ -17899,7 +17899,7 @@
         <v>0</v>
       </c>
       <c r="CO37" t="n">
-        <v>674.4526882366628</v>
+        <v>674.4526882366629</v>
       </c>
       <c r="CP37" t="n">
         <v>0</v>
@@ -19360,7 +19360,7 @@
         <v>0</v>
       </c>
       <c r="CO40" t="n">
-        <v>328.588871384768</v>
+        <v>328.5888713847681</v>
       </c>
       <c r="CP40" t="n">
         <v>0</v>
@@ -20334,7 +20334,7 @@
         <v>0</v>
       </c>
       <c r="CO42" t="n">
-        <v>622.9019437108894</v>
+        <v>622.9019437108896</v>
       </c>
       <c r="CP42" t="n">
         <v>0</v>
@@ -21308,7 +21308,7 @@
         <v>0</v>
       </c>
       <c r="CO44" t="n">
-        <v>1784.382208354206</v>
+        <v>1784.382208354207</v>
       </c>
       <c r="CP44" t="n">
         <v>0</v>
@@ -22276,13 +22276,13 @@
         <v>2476.526848987155</v>
       </c>
       <c r="CL46" t="n">
-        <v>2063.772374155962</v>
+        <v>2063.772374155963</v>
       </c>
       <c r="CN46" t="n">
         <v>0</v>
       </c>
       <c r="CO46" t="n">
-        <v>2063.772374155962</v>
+        <v>2063.772374155963</v>
       </c>
       <c r="CP46" t="n">
         <v>0</v>
@@ -23259,7 +23259,7 @@
         <v>1949.463719306847</v>
       </c>
       <c r="CP48" t="n">
-        <v>0.6385914517290571</v>
+        <v>0.6385914517290568</v>
       </c>
       <c r="CR48" t="n">
         <v>1130.688957197971</v>
@@ -23298,7 +23298,7 @@
         <v>0</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.6385914517290571</v>
+        <v>0.6385914517290568</v>
       </c>
       <c r="DF48" t="n">
         <v>0</v>
@@ -23734,7 +23734,7 @@
         <v>3.332260736610822</v>
       </c>
       <c r="CK49" t="n">
-        <v>7002.158950380315</v>
+        <v>7002.158950380317</v>
       </c>
       <c r="CL49" t="n">
         <v>1283.79963803015</v>
@@ -23746,10 +23746,10 @@
         <v>1283.79963803015</v>
       </c>
       <c r="CP49" t="n">
-        <v>0.3853569105261551</v>
+        <v>0.385356910526155</v>
       </c>
       <c r="CR49" t="n">
-        <v>449.3298733105524</v>
+        <v>449.3298733105525</v>
       </c>
       <c r="CS49" t="n">
         <v>0</v>
@@ -23785,7 +23785,7 @@
         <v>0</v>
       </c>
       <c r="DE49" t="n">
-        <v>0.3853569105261551</v>
+        <v>0.385356910526155</v>
       </c>
       <c r="DF49" t="n">
         <v>0</v>
@@ -23914,13 +23914,13 @@
         <v>1173.129812779892</v>
       </c>
       <c r="FB49" t="n">
-        <v>476.3193181600352</v>
+        <v>476.3193181600353</v>
       </c>
       <c r="FC49" t="n">
         <v>1173.129812779892</v>
       </c>
       <c r="FD49" t="n">
-        <v>0.4060243913086918</v>
+        <v>0.4060243913086919</v>
       </c>
       <c r="FF49" t="n">
         <v>410.5954344729621</v>
@@ -23947,7 +23947,7 @@
         <v>0</v>
       </c>
       <c r="FO49" t="n">
-        <v>476.3193181600352</v>
+        <v>476.3193181600353</v>
       </c>
       <c r="FP49" t="n">
         <v>0</v>
@@ -23959,7 +23959,7 @@
         <v>0</v>
       </c>
       <c r="FS49" t="n">
-        <v>0.4060243913086918</v>
+        <v>0.4060243913086919</v>
       </c>
       <c r="FT49" t="n">
         <v>0</v>
@@ -24230,7 +24230,7 @@
         <v>0</v>
       </c>
       <c r="CO50" t="n">
-        <v>67.17782467421232</v>
+        <v>67.17782467421233</v>
       </c>
       <c r="CP50" t="n">
         <v>0</v>
@@ -24717,7 +24717,7 @@
         <v>0</v>
       </c>
       <c r="CO51" t="n">
-        <v>22.39260822473743</v>
+        <v>22.39260822473744</v>
       </c>
       <c r="CP51" t="n">
         <v>0</v>
@@ -27143,22 +27143,22 @@
         <v>0.4933952551764867</v>
       </c>
       <c r="CK56" t="n">
-        <v>315.7457828283667</v>
+        <v>315.7457828283668</v>
       </c>
       <c r="CL56" t="n">
-        <v>216.8117093601975</v>
+        <v>216.8117093601976</v>
       </c>
       <c r="CN56" t="n">
         <v>94.07833404554817</v>
       </c>
       <c r="CO56" t="n">
-        <v>216.8117093601975</v>
+        <v>216.8117093601976</v>
       </c>
       <c r="CP56" t="n">
-        <v>0.4339172193382428</v>
+        <v>0.4339172193382427</v>
       </c>
       <c r="CR56" t="n">
-        <v>85.44654582938119</v>
+        <v>85.44654582938121</v>
       </c>
       <c r="CS56" t="n">
         <v>0</v>
@@ -27194,7 +27194,7 @@
         <v>0</v>
       </c>
       <c r="DE56" t="n">
-        <v>0.4339172193382428</v>
+        <v>0.4339172193382427</v>
       </c>
       <c r="DF56" t="n">
         <v>0</v>
@@ -27462,16 +27462,16 @@
         <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>570.1002751745827</v>
+        <v>570.1002751745825</v>
       </c>
       <c r="AA57" t="n">
         <v>835.1737112224071</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.6826128115792247</v>
+        <v>0.6826128115792244</v>
       </c>
       <c r="AD57" t="n">
-        <v>551.2146494067888</v>
+        <v>551.2146494067886</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -27483,7 +27483,7 @@
         <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>0.6600000000000001</v>
+        <v>0.6599999999999999</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -27495,7 +27495,7 @@
         <v>0</v>
       </c>
       <c r="AM57" t="n">
-        <v>570.1002751745827</v>
+        <v>570.1002751745825</v>
       </c>
       <c r="AN57" t="n">
         <v>0</v>
@@ -27507,7 +27507,7 @@
         <v>0</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.6826128115792247</v>
+        <v>0.6826128115792244</v>
       </c>
       <c r="AR57" t="n">
         <v>0</v>
@@ -27609,10 +27609,10 @@
         <v>280.4626365994912</v>
       </c>
       <c r="CD57" t="n">
-        <v>3.515872663704184</v>
+        <v>3.515872663704185</v>
       </c>
       <c r="CE57" t="n">
-        <v>0.006988510755803239</v>
+        <v>0.00698851075580324</v>
       </c>
       <c r="CF57" t="n">
         <v>2284.180265136335</v>
@@ -27624,7 +27624,7 @@
         <v>0</v>
       </c>
       <c r="CI57" t="n">
-        <v>3.515872663704184</v>
+        <v>3.515872663704185</v>
       </c>
       <c r="CJ57" t="n">
         <v>0</v>
@@ -28117,22 +28117,22 @@
         <v>2.190095444630908</v>
       </c>
       <c r="CK58" t="n">
-        <v>1791.637670472904</v>
+        <v>1791.637670472905</v>
       </c>
       <c r="CL58" t="n">
         <v>1501.755455428377</v>
       </c>
       <c r="CN58" t="n">
-        <v>876.3350760426559</v>
+        <v>876.3350760426561</v>
       </c>
       <c r="CO58" t="n">
         <v>1501.755455428377</v>
       </c>
       <c r="CP58" t="n">
-        <v>0.5835404645110349</v>
+        <v>0.5835404645110348</v>
       </c>
       <c r="CR58" t="n">
-        <v>795.9303913770399</v>
+        <v>795.9303913770401</v>
       </c>
       <c r="CS58" t="n">
         <v>0</v>
@@ -28156,7 +28156,7 @@
         <v>0</v>
       </c>
       <c r="DA58" t="n">
-        <v>876.3350760426559</v>
+        <v>876.3350760426561</v>
       </c>
       <c r="DB58" t="n">
         <v>0</v>
@@ -28168,7 +28168,7 @@
         <v>0</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.5835404645110349</v>
+        <v>0.5835404645110348</v>
       </c>
       <c r="DF58" t="n">
         <v>0</v>
@@ -28604,22 +28604,22 @@
         <v>0.8449310989503658</v>
       </c>
       <c r="CK59" t="n">
-        <v>923.0113245036678</v>
+        <v>923.011324503668</v>
       </c>
       <c r="CL59" t="n">
-        <v>773.6743040385894</v>
+        <v>773.6743040385896</v>
       </c>
       <c r="CN59" t="n">
-        <v>451.4702627589301</v>
+        <v>451.4702627589302</v>
       </c>
       <c r="CO59" t="n">
-        <v>773.6743040385894</v>
+        <v>773.6743040385896</v>
       </c>
       <c r="CP59" t="n">
         <v>0.5835404645110349</v>
       </c>
       <c r="CR59" t="n">
-        <v>410.0473811404524</v>
+        <v>410.0473811404526</v>
       </c>
       <c r="CS59" t="n">
         <v>0</v>
@@ -28643,7 +28643,7 @@
         <v>0</v>
       </c>
       <c r="DA59" t="n">
-        <v>451.4702627589301</v>
+        <v>451.4702627589302</v>
       </c>
       <c r="DB59" t="n">
         <v>0</v>
@@ -30065,16 +30065,16 @@
         <v>4.779874123211328</v>
       </c>
       <c r="CK62" t="n">
-        <v>2706.268852086857</v>
+        <v>2706.268852086858</v>
       </c>
       <c r="CL62" t="n">
-        <v>2255.224043405714</v>
+        <v>2255.224043405715</v>
       </c>
       <c r="CN62" t="n">
         <v>0</v>
       </c>
       <c r="CO62" t="n">
-        <v>2255.224043405714</v>
+        <v>2255.224043405715</v>
       </c>
       <c r="CP62" t="n">
         <v>0</v>
@@ -30552,16 +30552,16 @@
         <v>0.1188889374855213</v>
       </c>
       <c r="CK63" t="n">
-        <v>92.78268687855085</v>
+        <v>92.78268687855086</v>
       </c>
       <c r="CL63" t="n">
-        <v>77.3189057321257</v>
+        <v>77.31890573212571</v>
       </c>
       <c r="CN63" t="n">
         <v>0</v>
       </c>
       <c r="CO63" t="n">
-        <v>77.3189057321257</v>
+        <v>77.31890573212571</v>
       </c>
       <c r="CP63" t="n">
         <v>0</v>
@@ -31039,16 +31039,16 @@
         <v>4.965643378388648</v>
       </c>
       <c r="CK64" t="n">
-        <v>9926.044450379592</v>
+        <v>9926.044450379593</v>
       </c>
       <c r="CL64" t="n">
-        <v>8271.703708649658</v>
+        <v>8271.70370864966</v>
       </c>
       <c r="CN64" t="n">
         <v>0</v>
       </c>
       <c r="CO64" t="n">
-        <v>8271.703708649658</v>
+        <v>8271.70370864966</v>
       </c>
       <c r="CP64" t="n">
         <v>0</v>
@@ -32022,7 +32022,7 @@
         <v>0</v>
       </c>
       <c r="CO66" t="n">
-        <v>1661.392297596477</v>
+        <v>1661.392297596478</v>
       </c>
       <c r="CP66" t="n">
         <v>0</v>
@@ -32512,10 +32512,10 @@
         <v>10828.10255485673</v>
       </c>
       <c r="CP67" t="n">
-        <v>0.6385914517290571</v>
+        <v>0.638591451729057</v>
       </c>
       <c r="CR67" t="n">
-        <v>6280.299481816904</v>
+        <v>6280.299481816905</v>
       </c>
       <c r="CS67" t="n">
         <v>0</v>
@@ -32551,7 +32551,7 @@
         <v>0</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.6385914517290571</v>
+        <v>0.638591451729057</v>
       </c>
       <c r="DF67" t="n">
         <v>0</v>
@@ -32680,13 +32680,13 @@
         <v>12498.95719685697</v>
       </c>
       <c r="FB67" t="n">
-        <v>8409.803608432576</v>
+        <v>8409.803608432578</v>
       </c>
       <c r="FC67" t="n">
         <v>12498.95719685697</v>
       </c>
       <c r="FD67" t="n">
-        <v>0.6728404198829749</v>
+        <v>0.672840419882975</v>
       </c>
       <c r="FF67" t="n">
         <v>7249.395174177042</v>
@@ -32713,7 +32713,7 @@
         <v>0</v>
       </c>
       <c r="FO67" t="n">
-        <v>8409.803608432576</v>
+        <v>8409.803608432578</v>
       </c>
       <c r="FP67" t="n">
         <v>0</v>
@@ -32725,7 +32725,7 @@
         <v>0</v>
       </c>
       <c r="FS67" t="n">
-        <v>0.6728404198829749</v>
+        <v>0.672840419882975</v>
       </c>
       <c r="FT67" t="n">
         <v>0</v>
@@ -32996,7 +32996,7 @@
         <v>0</v>
       </c>
       <c r="CO68" t="n">
-        <v>58.22878841851133</v>
+        <v>58.22878841851134</v>
       </c>
       <c r="CP68" t="n">
         <v>0</v>
@@ -33483,7 +33483,7 @@
         <v>0</v>
       </c>
       <c r="CO69" t="n">
-        <v>262.029547883301</v>
+        <v>262.0295478833011</v>
       </c>
       <c r="CP69" t="n">
         <v>0</v>
@@ -34935,7 +34935,7 @@
         <v>0.04320266092565415</v>
       </c>
       <c r="CK72" t="n">
-        <v>142.5534017559796</v>
+        <v>142.5534017559797</v>
       </c>
       <c r="CL72" t="n">
         <v>120.8373108214407</v>
@@ -34947,10 +34947,10 @@
         <v>120.8373108214407</v>
       </c>
       <c r="CP72" t="n">
-        <v>0.558547316314053</v>
+        <v>0.5585473163140527</v>
       </c>
       <c r="CR72" t="n">
-        <v>61.30076777971685</v>
+        <v>61.30076777971686</v>
       </c>
       <c r="CS72" t="n">
         <v>0</v>
@@ -34986,7 +34986,7 @@
         <v>0</v>
       </c>
       <c r="DE72" t="n">
-        <v>0.558547316314053</v>
+        <v>0.5585473163140527</v>
       </c>
       <c r="DF72" t="n">
         <v>0</v>
@@ -35115,13 +35115,13 @@
         <v>73.73510876900642</v>
       </c>
       <c r="FB72" t="n">
-        <v>35.50745477097214</v>
+        <v>35.50745477097215</v>
       </c>
       <c r="FC72" t="n">
         <v>73.73510876900642</v>
       </c>
       <c r="FD72" t="n">
-        <v>0.481554246867772</v>
+        <v>0.4815542468677722</v>
       </c>
       <c r="FF72" t="n">
         <v>30.60803596006575</v>
@@ -35148,7 +35148,7 @@
         <v>0</v>
       </c>
       <c r="FO72" t="n">
-        <v>35.50745477097214</v>
+        <v>35.50745477097215</v>
       </c>
       <c r="FP72" t="n">
         <v>0</v>
@@ -35160,7 +35160,7 @@
         <v>0</v>
       </c>
       <c r="FS72" t="n">
-        <v>0.481554246867772</v>
+        <v>0.4815542468677722</v>
       </c>
       <c r="FT72" t="n">
         <v>0</v>
@@ -35422,22 +35422,22 @@
         <v>8.507163971186191</v>
       </c>
       <c r="CK73" t="n">
-        <v>5406.079231685695</v>
+        <v>5406.079231685696</v>
       </c>
       <c r="CL73" t="n">
-        <v>4565.623893696391</v>
+        <v>4565.623893696393</v>
       </c>
       <c r="CN73" t="n">
         <v>3267.447333984296</v>
       </c>
       <c r="CO73" t="n">
-        <v>4565.623893696391</v>
+        <v>4565.623893696393</v>
       </c>
       <c r="CP73" t="n">
-        <v>0.7156628338342882</v>
+        <v>0.715662833834288</v>
       </c>
       <c r="CR73" t="n">
-        <v>2967.655530902654</v>
+        <v>2967.655530902655</v>
       </c>
       <c r="CS73" t="n">
         <v>0</v>
@@ -35473,7 +35473,7 @@
         <v>0</v>
       </c>
       <c r="DE73" t="n">
-        <v>0.7156628338342882</v>
+        <v>0.715662833834288</v>
       </c>
       <c r="DF73" t="n">
         <v>0</v>
@@ -35912,13 +35912,13 @@
         <v>1103.249965433116</v>
       </c>
       <c r="CL74" t="n">
-        <v>919.3749711942631</v>
+        <v>919.3749711942634</v>
       </c>
       <c r="CN74" t="n">
         <v>0</v>
       </c>
       <c r="CO74" t="n">
-        <v>919.3749711942631</v>
+        <v>919.3749711942634</v>
       </c>
       <c r="CP74" t="n">
         <v>0</v>
@@ -37370,16 +37370,16 @@
         <v>3.176303460666167</v>
       </c>
       <c r="CK77" t="n">
-        <v>6518.478043338159</v>
+        <v>6518.478043338161</v>
       </c>
       <c r="CL77" t="n">
-        <v>5432.065036115133</v>
+        <v>5432.065036115134</v>
       </c>
       <c r="CN77" t="n">
         <v>0</v>
       </c>
       <c r="CO77" t="n">
-        <v>5432.065036115133</v>
+        <v>5432.065036115134</v>
       </c>
       <c r="CP77" t="n">
         <v>0</v>
@@ -38344,22 +38344,22 @@
         <v>3.335167640853874</v>
       </c>
       <c r="CK79" t="n">
-        <v>2362.872442864682</v>
+        <v>2362.872442864683</v>
       </c>
       <c r="CL79" t="n">
-        <v>2004.422859284841</v>
+        <v>2004.422859284842</v>
       </c>
       <c r="CN79" t="n">
         <v>1081.385480618812</v>
       </c>
       <c r="CO79" t="n">
-        <v>2004.422859284841</v>
+        <v>2004.422859284842</v>
       </c>
       <c r="CP79" t="n">
-        <v>0.5394996747366172</v>
+        <v>0.5394996747366171</v>
       </c>
       <c r="CR79" t="n">
-        <v>982.1672010495723</v>
+        <v>982.1672010495726</v>
       </c>
       <c r="CS79" t="n">
         <v>0</v>
@@ -38395,7 +38395,7 @@
         <v>0</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.5394996747366172</v>
+        <v>0.5394996747366171</v>
       </c>
       <c r="DF79" t="n">
         <v>0</v>
@@ -38509,7 +38509,7 @@
         <v>1577.085018426687</v>
       </c>
       <c r="EV79" t="n">
-        <v>0.01829235857247885</v>
+        <v>0.01829235857247886</v>
       </c>
       <c r="EW79" t="n">
         <v>0</v>
@@ -38524,13 +38524,13 @@
         <v>1565.399814056458</v>
       </c>
       <c r="FB79" t="n">
-        <v>693.346449309479</v>
+        <v>693.3464493094791</v>
       </c>
       <c r="FC79" t="n">
         <v>1565.399814056458</v>
       </c>
       <c r="FD79" t="n">
-        <v>0.4429197212645592</v>
+        <v>0.4429197212645593</v>
       </c>
       <c r="FF79" t="n">
         <v>597.676549618468</v>
@@ -38557,7 +38557,7 @@
         <v>0</v>
       </c>
       <c r="FO79" t="n">
-        <v>693.346449309479</v>
+        <v>693.3464493094791</v>
       </c>
       <c r="FP79" t="n">
         <v>0</v>
@@ -38569,7 +38569,7 @@
         <v>0</v>
       </c>
       <c r="FS79" t="n">
-        <v>0.4429197212645592</v>
+        <v>0.4429197212645593</v>
       </c>
       <c r="FT79" t="n">
         <v>0</v>
@@ -38840,7 +38840,7 @@
         <v>0</v>
       </c>
       <c r="CO80" t="n">
-        <v>25464.19868061738</v>
+        <v>25464.19868061739</v>
       </c>
       <c r="CP80" t="n">
         <v>0</v>
@@ -39327,7 +39327,7 @@
         <v>0</v>
       </c>
       <c r="CO81" t="n">
-        <v>9167.111525022259</v>
+        <v>9167.111525022261</v>
       </c>
       <c r="CP81" t="n">
         <v>0</v>
@@ -39814,7 +39814,7 @@
         <v>0</v>
       </c>
       <c r="CO82" t="n">
-        <v>6111.407683348173</v>
+        <v>6111.407683348175</v>
       </c>
       <c r="CP82" t="n">
         <v>0</v>
@@ -40109,7 +40109,7 @@
         <v>6833.074542652652</v>
       </c>
       <c r="T83" t="n">
-        <v>0.01572426167562822</v>
+        <v>0.01572426167562821</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -40292,22 +40292,22 @@
         <v>4.844086411554377</v>
       </c>
       <c r="CK83" t="n">
-        <v>9418.922122159156</v>
+        <v>9418.922122159158</v>
       </c>
       <c r="CL83" t="n">
-        <v>7988.644515286914</v>
+        <v>7988.644515286916</v>
       </c>
       <c r="CN83" t="n">
         <v>5365.349758624669</v>
       </c>
       <c r="CO83" t="n">
-        <v>7988.644515286914</v>
+        <v>7988.644515286916</v>
       </c>
       <c r="CP83" t="n">
-        <v>0.6716220440598704</v>
+        <v>0.6716220440598702</v>
       </c>
       <c r="CR83" t="n">
-        <v>4873.073154325018</v>
+        <v>4873.073154325019</v>
       </c>
       <c r="CS83" t="n">
         <v>0</v>
@@ -40343,7 +40343,7 @@
         <v>0</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.6716220440598704</v>
+        <v>0.6716220440598702</v>
       </c>
       <c r="DF83" t="n">
         <v>0</v>
@@ -40457,7 +40457,7 @@
         <v>2402.26135972568</v>
       </c>
       <c r="EV83" t="n">
-        <v>0.004815767202100152</v>
+        <v>0.004815767202100153</v>
       </c>
       <c r="EW83" t="n">
         <v>0</v>
@@ -40779,7 +40779,7 @@
         <v>3.360220406489543</v>
       </c>
       <c r="CK84" t="n">
-        <v>7141.864867470007</v>
+        <v>7141.864867470009</v>
       </c>
       <c r="CL84" t="n">
         <v>6058.438423753712</v>
@@ -40794,7 +40794,7 @@
         <v>0.5394996747366171</v>
       </c>
       <c r="CR84" t="n">
-        <v>2968.634827639318</v>
+        <v>2968.634827639319</v>
       </c>
       <c r="CS84" t="n">
         <v>0</v>
@@ -40959,13 +40959,13 @@
         <v>4731.402692783491</v>
       </c>
       <c r="FB84" t="n">
-        <v>2095.631561878048</v>
+        <v>2095.631561878049</v>
       </c>
       <c r="FC84" t="n">
         <v>4731.402692783491</v>
       </c>
       <c r="FD84" t="n">
-        <v>0.4429197212645591</v>
+        <v>0.4429197212645592</v>
       </c>
       <c r="FF84" t="n">
         <v>1806.470405123209</v>
@@ -40992,7 +40992,7 @@
         <v>0</v>
       </c>
       <c r="FO84" t="n">
-        <v>2095.631561878048</v>
+        <v>2095.631561878049</v>
       </c>
       <c r="FP84" t="n">
         <v>0</v>
@@ -41004,7 +41004,7 @@
         <v>0</v>
       </c>
       <c r="FS84" t="n">
-        <v>0.4429197212645591</v>
+        <v>0.4429197212645592</v>
       </c>
       <c r="FT84" t="n">
         <v>0</v>
@@ -41275,7 +41275,7 @@
         <v>0</v>
       </c>
       <c r="CO85" t="n">
-        <v>16.33416258296613</v>
+        <v>16.33416258296614</v>
       </c>
       <c r="CP85" t="n">
         <v>0</v>
@@ -41762,7 +41762,7 @@
         <v>0</v>
       </c>
       <c r="CO86" t="n">
-        <v>37.18369386933214</v>
+        <v>37.18369386933215</v>
       </c>
       <c r="CP86" t="n">
         <v>0</v>
@@ -43223,10 +43223,10 @@
         <v>3111.735138017975</v>
       </c>
       <c r="CO89" t="n">
-        <v>8008.778022617046</v>
+        <v>8008.778022617048</v>
       </c>
       <c r="CP89" t="n">
-        <v>0.3885405650188249</v>
+        <v>0.3885405650188248</v>
       </c>
       <c r="CR89" t="n">
         <v>2803.072307915966</v>
@@ -43238,7 +43238,7 @@
         <v>0</v>
       </c>
       <c r="CU89" t="n">
-        <v>28.55172839148048</v>
+        <v>28.55172839148049</v>
       </c>
       <c r="CV89" t="n">
         <v>0.3499999999999999</v>
@@ -43262,10 +43262,10 @@
         <v>0</v>
       </c>
       <c r="DD89" t="n">
-        <v>25.49718213250069</v>
+        <v>25.4971821325007</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.3853569105261551</v>
+        <v>0.3853569105261549</v>
       </c>
       <c r="DF89" t="n">
         <v>0</v>
@@ -43274,7 +43274,7 @@
         <v>0</v>
       </c>
       <c r="DH89" t="n">
-        <v>0.003183654492669896</v>
+        <v>0.003183654492669897</v>
       </c>
       <c r="DJ89" t="n">
         <v>483.9301367509202</v>
@@ -43394,7 +43394,7 @@
         <v>0</v>
       </c>
       <c r="FB89" t="n">
-        <v>7363.978784276296</v>
+        <v>7363.978784276297</v>
       </c>
       <c r="FC89" t="n">
         <v>17801.25870872436</v>
@@ -43710,10 +43710,10 @@
         <v>3111.735138017975</v>
       </c>
       <c r="CO90" t="n">
-        <v>8008.778022617046</v>
+        <v>8008.778022617048</v>
       </c>
       <c r="CP90" t="n">
-        <v>0.3885405650188249</v>
+        <v>0.3885405650188248</v>
       </c>
       <c r="CR90" t="n">
         <v>2803.072307915966</v>
@@ -43725,7 +43725,7 @@
         <v>0</v>
       </c>
       <c r="CU90" t="n">
-        <v>28.55172839148048</v>
+        <v>28.55172839148049</v>
       </c>
       <c r="CV90" t="n">
         <v>0.3499999999999999</v>
@@ -43749,10 +43749,10 @@
         <v>0</v>
       </c>
       <c r="DD90" t="n">
-        <v>25.49718213250069</v>
+        <v>25.4971821325007</v>
       </c>
       <c r="DE90" t="n">
-        <v>0.3853569105261551</v>
+        <v>0.3853569105261549</v>
       </c>
       <c r="DF90" t="n">
         <v>0</v>
@@ -43761,7 +43761,7 @@
         <v>0</v>
       </c>
       <c r="DH90" t="n">
-        <v>0.003183654492669896</v>
+        <v>0.003183654492669897</v>
       </c>
       <c r="DJ90" t="n">
         <v>483.9301367509202</v>
@@ -43881,7 +43881,7 @@
         <v>0</v>
       </c>
       <c r="FB90" t="n">
-        <v>7363.978784276296</v>
+        <v>7363.978784276297</v>
       </c>
       <c r="FC90" t="n">
         <v>17801.25870872436</v>
@@ -44197,7 +44197,7 @@
         <v>0</v>
       </c>
       <c r="CO91" t="n">
-        <v>7689.368988834219</v>
+        <v>7689.368988834221</v>
       </c>
       <c r="CP91" t="n">
         <v>0</v>
@@ -44684,7 +44684,7 @@
         <v>0</v>
       </c>
       <c r="CO92" t="n">
-        <v>373.7640471391623</v>
+        <v>373.7640471391624</v>
       </c>
       <c r="CP92" t="n">
         <v>0</v>
@@ -45162,16 +45162,16 @@
         <v>6.301862452540859</v>
       </c>
       <c r="CK93" t="n">
-        <v>6563.330953411394</v>
+        <v>6563.330953411396</v>
       </c>
       <c r="CL93" t="n">
-        <v>5469.442461176162</v>
+        <v>5469.442461176163</v>
       </c>
       <c r="CN93" t="n">
         <v>0</v>
       </c>
       <c r="CO93" t="n">
-        <v>5469.442461176162</v>
+        <v>5469.442461176163</v>
       </c>
       <c r="CP93" t="n">
         <v>0</v>
@@ -45466,7 +45466,7 @@
         <v>2873.607910446671</v>
       </c>
       <c r="T94" t="n">
-        <v>0.005685636002962187</v>
+        <v>0.005685636002962185</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -45640,7 +45640,7 @@
         <v>1287.558942313842</v>
       </c>
       <c r="CH94" t="n">
-        <v>0.002244125786996597</v>
+        <v>0.002244125786996598</v>
       </c>
       <c r="CI94" t="n">
         <v>0</v>
@@ -45652,19 +45652,19 @@
         <v>1490.997708618458</v>
       </c>
       <c r="CL94" t="n">
-        <v>1284.863757567798</v>
+        <v>1284.863757567799</v>
       </c>
       <c r="CN94" t="n">
         <v>544.259296939504</v>
       </c>
       <c r="CO94" t="n">
-        <v>1284.863757567798</v>
+        <v>1284.863757567799</v>
       </c>
       <c r="CP94" t="n">
-        <v>0.423593002552868</v>
+        <v>0.4235930025528679</v>
       </c>
       <c r="CR94" t="n">
-        <v>474.7228465088954</v>
+        <v>474.7228465088955</v>
       </c>
       <c r="CS94" t="n">
         <v>0</v>
@@ -45673,7 +45673,7 @@
         <v>0</v>
       </c>
       <c r="CU94" t="n">
-        <v>24.16534852258758</v>
+        <v>24.16534852258759</v>
       </c>
       <c r="CV94" t="n">
         <v>0.3694732952912681</v>
@@ -45697,10 +45697,10 @@
         <v>0</v>
       </c>
       <c r="DD94" t="n">
-        <v>21.58006983421794</v>
+        <v>21.58006983421795</v>
       </c>
       <c r="DE94" t="n">
-        <v>0.4067973931296026</v>
+        <v>0.4067973931296025</v>
       </c>
       <c r="DF94" t="n">
         <v>0</v>
@@ -46136,22 +46136,22 @@
         <v>0.392241519476917</v>
       </c>
       <c r="CK95" t="n">
-        <v>298.6093347248492</v>
+        <v>298.6093347248494</v>
       </c>
       <c r="CL95" t="n">
-        <v>257.3240035842471</v>
+        <v>257.3240035842472</v>
       </c>
       <c r="CN95" t="n">
         <v>108.9992457276499</v>
       </c>
       <c r="CO95" t="n">
-        <v>257.3240035842471</v>
+        <v>257.3240035842472</v>
       </c>
       <c r="CP95" t="n">
         <v>0.42358755580283</v>
       </c>
       <c r="CR95" t="n">
-        <v>95.07434756181387</v>
+        <v>95.07434756181389</v>
       </c>
       <c r="CS95" t="n">
         <v>0</v>
@@ -46160,7 +46160,7 @@
         <v>0</v>
       </c>
       <c r="CU95" t="n">
-        <v>4.838106464713607</v>
+        <v>4.838106464713608</v>
       </c>
       <c r="CV95" t="n">
         <v>0.3694732952912681</v>
@@ -46184,10 +46184,10 @@
         <v>0</v>
       </c>
       <c r="DD95" t="n">
-        <v>4.320511879905684</v>
+        <v>4.320511879905686</v>
       </c>
       <c r="DE95" t="n">
-        <v>0.4067973931296026</v>
+        <v>0.4067973931296025</v>
       </c>
       <c r="DF95" t="n">
         <v>0</v>
@@ -46623,19 +46623,19 @@
         <v>3.81803960133443</v>
       </c>
       <c r="CK96" t="n">
-        <v>4002.024515545169</v>
+        <v>4002.02451554517</v>
       </c>
       <c r="CL96" t="n">
-        <v>3295.16613866144</v>
+        <v>3295.166138661441</v>
       </c>
       <c r="CN96" t="n">
         <v>2104.26492817624</v>
       </c>
       <c r="CO96" t="n">
-        <v>3295.16613866144</v>
+        <v>3295.166138661441</v>
       </c>
       <c r="CP96" t="n">
-        <v>0.638591451729057</v>
+        <v>0.6385914517290568</v>
       </c>
       <c r="CR96" t="n">
         <v>1911.196360423635</v>
@@ -46674,7 +46674,7 @@
         <v>0</v>
       </c>
       <c r="DE96" t="n">
-        <v>0.638591451729057</v>
+        <v>0.6385914517290568</v>
       </c>
       <c r="DF96" t="n">
         <v>0</v>
@@ -47119,7 +47119,7 @@
         <v>0</v>
       </c>
       <c r="CO97" t="n">
-        <v>17.48720569496544</v>
+        <v>17.48720569496545</v>
       </c>
       <c r="CP97" t="n">
         <v>0</v>
@@ -47606,7 +47606,7 @@
         <v>0</v>
       </c>
       <c r="CO98" t="n">
-        <v>675.6368202362261</v>
+        <v>675.6368202362262</v>
       </c>
       <c r="CP98" t="n">
         <v>0</v>
@@ -48084,16 +48084,16 @@
         <v>1.413070569041377</v>
       </c>
       <c r="CK99" t="n">
-        <v>50.53245967030794</v>
+        <v>50.53245967030795</v>
       </c>
       <c r="CL99" t="n">
-        <v>42.11038305858995</v>
+        <v>42.11038305858996</v>
       </c>
       <c r="CN99" t="n">
         <v>0</v>
       </c>
       <c r="CO99" t="n">
-        <v>42.11038305858995</v>
+        <v>42.11038305858996</v>
       </c>
       <c r="CP99" t="n">
         <v>0</v>
@@ -48571,16 +48571,16 @@
         <v>1.994482448766457</v>
       </c>
       <c r="CK100" t="n">
-        <v>5264.055736693821</v>
+        <v>5264.055736693822</v>
       </c>
       <c r="CL100" t="n">
-        <v>4386.713113911518</v>
+        <v>4386.713113911519</v>
       </c>
       <c r="CN100" t="n">
         <v>0</v>
       </c>
       <c r="CO100" t="n">
-        <v>4386.713113911518</v>
+        <v>4386.713113911519</v>
       </c>
       <c r="CP100" t="n">
         <v>0</v>
@@ -48980,7 +48980,7 @@
         <v>0</v>
       </c>
       <c r="BH101" t="n">
-        <v>1711.675345423301</v>
+        <v>1711.6753454233</v>
       </c>
       <c r="BI101" t="n">
         <v>0</v>
@@ -49067,7 +49067,7 @@
         <v>0</v>
       </c>
       <c r="CO101" t="n">
-        <v>244.7363033975127</v>
+        <v>244.7363033975126</v>
       </c>
       <c r="CP101" t="n">
         <v>0</v>
@@ -49154,7 +49154,7 @@
         <v>0</v>
       </c>
       <c r="DV101" t="n">
-        <v>77.80498278593767</v>
+        <v>77.80498278593764</v>
       </c>
       <c r="DW101" t="n">
         <v>0</v>
@@ -49241,7 +49241,7 @@
         <v>0</v>
       </c>
       <c r="FC101" t="n">
-        <v>26.75124223546307</v>
+        <v>26.75124223546306</v>
       </c>
       <c r="FD101" t="n">
         <v>0</v>
@@ -50041,7 +50041,7 @@
         <v>0</v>
       </c>
       <c r="CO103" t="n">
-        <v>38.56882367368596</v>
+        <v>38.56882367368597</v>
       </c>
       <c r="CP103" t="n">
         <v>0</v>
@@ -51015,7 +51015,7 @@
         <v>0</v>
       </c>
       <c r="CO105" t="n">
-        <v>82.64785933157718</v>
+        <v>82.64785933157719</v>
       </c>
       <c r="CP105" t="n">
         <v>0</v>
@@ -51502,7 +51502,7 @@
         <v>0</v>
       </c>
       <c r="CO106" t="n">
-        <v>688.7289941729634</v>
+        <v>688.7289941729636</v>
       </c>
       <c r="CP106" t="n">
         <v>0</v>
@@ -51989,7 +51989,7 @@
         <v>0</v>
       </c>
       <c r="CO107" t="n">
-        <v>88831.16691339489</v>
+        <v>88831.16691339486</v>
       </c>
       <c r="CP107" t="n">
         <v>0</v>
@@ -52076,7 +52076,7 @@
         <v>0</v>
       </c>
       <c r="DV107" t="n">
-        <v>64578.0628470822</v>
+        <v>64578.06284708219</v>
       </c>
       <c r="DW107" t="n">
         <v>0</v>
@@ -52163,7 +52163,7 @@
         <v>0</v>
       </c>
       <c r="FC107" t="n">
-        <v>65040.018335299</v>
+        <v>65040.01833529899</v>
       </c>
       <c r="FD107" t="n">
         <v>0</v>
@@ -52476,7 +52476,7 @@
         <v>0</v>
       </c>
       <c r="CO108" t="n">
-        <v>7402.597242782908</v>
+        <v>7402.597242782906</v>
       </c>
       <c r="CP108" t="n">
         <v>0</v>
@@ -52563,7 +52563,7 @@
         <v>0</v>
       </c>
       <c r="DV108" t="n">
-        <v>5381.505237256852</v>
+        <v>5381.50523725685</v>
       </c>
       <c r="DW108" t="n">
         <v>0</v>
@@ -52954,16 +52954,16 @@
         <v>0.9972412243832286</v>
       </c>
       <c r="CK109" t="n">
-        <v>675.9323052418686</v>
+        <v>675.9323052418688</v>
       </c>
       <c r="CL109" t="n">
-        <v>563.2769210348905</v>
+        <v>563.2769210348906</v>
       </c>
       <c r="CN109" t="n">
         <v>0</v>
       </c>
       <c r="CO109" t="n">
-        <v>563.2769210348905</v>
+        <v>563.2769210348906</v>
       </c>
       <c r="CP109" t="n">
         <v>0</v>
@@ -53937,7 +53937,7 @@
         <v>0</v>
       </c>
       <c r="CO111" t="n">
-        <v>78.53494026805707</v>
+        <v>78.53494026805708</v>
       </c>
       <c r="CP111" t="n">
         <v>0</v>
@@ -54728,13 +54728,13 @@
         <v>3.256118303695876</v>
       </c>
       <c r="W113" t="n">
-        <v>4010.069181328577</v>
+        <v>4010.069181328576</v>
       </c>
       <c r="X113" t="n">
         <v>2201.189363504435</v>
       </c>
       <c r="Z113" t="n">
-        <v>377.1536779762753</v>
+        <v>377.1536779762752</v>
       </c>
       <c r="AA113" t="n">
         <v>2201.189363504435</v>
@@ -54743,7 +54743,7 @@
         <v>0.1713408597322233</v>
       </c>
       <c r="AD113" t="n">
-        <v>330.1784045256653</v>
+        <v>330.1784045256652</v>
       </c>
       <c r="AE113" t="n">
         <v>0</v>
@@ -54752,7 +54752,7 @@
         <v>0</v>
       </c>
       <c r="AG113" t="n">
-        <v>33.97467484116174</v>
+        <v>33.97467484116173</v>
       </c>
       <c r="AH113" t="n">
         <v>0.15</v>
@@ -54776,7 +54776,7 @@
         <v>0</v>
       </c>
       <c r="AP113" t="n">
-        <v>33.73423804940625</v>
+        <v>33.73423804940624</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.1560154004106776</v>
@@ -54815,19 +54815,19 @@
         <v>3.340712257225895</v>
       </c>
       <c r="BD113" t="n">
-        <v>4317.030999863201</v>
+        <v>4317.0309998632</v>
       </c>
       <c r="BE113" t="n">
         <v>2369.685481503211</v>
       </c>
       <c r="BG113" t="n">
-        <v>420.8653353023633</v>
+        <v>420.8653353023632</v>
       </c>
       <c r="BH113" t="n">
         <v>2369.685481503211</v>
       </c>
       <c r="BI113" t="n">
-        <v>0.1776038797500616</v>
+        <v>0.1776038797500617</v>
       </c>
       <c r="BK113" t="n">
         <v>355.4528222254817</v>
@@ -54839,7 +54839,7 @@
         <v>0</v>
       </c>
       <c r="BN113" t="n">
-        <v>36.57536014153654</v>
+        <v>36.57536014153653</v>
       </c>
       <c r="BO113" t="n">
         <v>0.15</v>
@@ -54866,7 +54866,7 @@
         <v>36.04203758128936</v>
       </c>
       <c r="BX113" t="n">
-        <v>0.162394250513347</v>
+        <v>0.1623942505133471</v>
       </c>
       <c r="BY113" t="n">
         <v>0</v>
@@ -54902,22 +54902,22 @@
         <v>3.442236502722989</v>
       </c>
       <c r="CK113" t="n">
-        <v>4664.444772544593</v>
+        <v>4664.444772544592</v>
       </c>
       <c r="CL113" t="n">
-        <v>2560.386306496926</v>
+        <v>2560.386306496925</v>
       </c>
       <c r="CN113" t="n">
-        <v>471.8771350261018</v>
+        <v>471.8771350261016</v>
       </c>
       <c r="CO113" t="n">
-        <v>2560.386306496926</v>
+        <v>2560.386306496925</v>
       </c>
       <c r="CP113" t="n">
         <v>0.184299194941296</v>
       </c>
       <c r="CR113" t="n">
-        <v>384.0579459745388</v>
+        <v>384.0579459745387</v>
       </c>
       <c r="CS113" t="n">
         <v>0</v>
@@ -54926,7 +54926,7 @@
         <v>0</v>
       </c>
       <c r="CU113" t="n">
-        <v>39.51876820470626</v>
+        <v>39.51876820470624</v>
       </c>
       <c r="CV113" t="n">
         <v>0.15</v>
@@ -54941,7 +54941,7 @@
         <v>0.01543468972023019</v>
       </c>
       <c r="DA113" t="n">
-        <v>433.2516486292362</v>
+        <v>433.2516486292359</v>
       </c>
       <c r="DB113" t="n">
         <v>0</v>
@@ -54950,7 +54950,7 @@
         <v>0</v>
       </c>
       <c r="DD113" t="n">
-        <v>38.62548639686565</v>
+        <v>38.62548639686563</v>
       </c>
       <c r="DE113" t="n">
         <v>0.1692133907800824</v>
@@ -54989,22 +54989,22 @@
         <v>3.512045058998211</v>
       </c>
       <c r="DR113" t="n">
-        <v>4989.854266175798</v>
+        <v>4989.854266175797</v>
       </c>
       <c r="DS113" t="n">
-        <v>2739.008640370741</v>
+        <v>2739.00864037074</v>
       </c>
       <c r="DU113" t="n">
-        <v>517.6115148301977</v>
+        <v>517.6115148301976</v>
       </c>
       <c r="DV113" t="n">
-        <v>2739.008640370741</v>
+        <v>2739.00864037074</v>
       </c>
       <c r="DW113" t="n">
         <v>0.1889776860142128</v>
       </c>
       <c r="DY113" t="n">
-        <v>410.8512960556112</v>
+        <v>410.851296055611</v>
       </c>
       <c r="DZ113" t="n">
         <v>0</v>
@@ -55013,7 +55013,7 @@
         <v>0</v>
       </c>
       <c r="EB113" t="n">
-        <v>42.27574850515145</v>
+        <v>42.27574850515144</v>
       </c>
       <c r="EC113" t="n">
         <v>0.15</v>
@@ -55028,7 +55028,7 @@
         <v>0.01543468972023001</v>
       </c>
       <c r="EH113" t="n">
-        <v>476.5283605751578</v>
+        <v>476.5283605751576</v>
       </c>
       <c r="EI113" t="n">
         <v>0</v>
@@ -55037,7 +55037,7 @@
         <v>0</v>
       </c>
       <c r="EK113" t="n">
-        <v>41.08315425504001</v>
+        <v>41.08315425504</v>
       </c>
       <c r="EL113" t="n">
         <v>0.1739784072059944</v>
@@ -55079,13 +55079,13 @@
         <v>5340.292248412674</v>
       </c>
       <c r="EZ113" t="n">
-        <v>2931.369501041032</v>
+        <v>2931.369501041031</v>
       </c>
       <c r="FB113" t="n">
-        <v>566.8123617146949</v>
+        <v>566.8123617146948</v>
       </c>
       <c r="FC113" t="n">
-        <v>2931.369501041032</v>
+        <v>2931.369501041031</v>
       </c>
       <c r="FD113" t="n">
         <v>0.193360939831502</v>
@@ -55100,7 +55100,7 @@
         <v>0</v>
       </c>
       <c r="FI113" t="n">
-        <v>45.24477870391406</v>
+        <v>45.24477870391405</v>
       </c>
       <c r="FJ113" t="n">
         <v>0.15</v>
@@ -55115,7 +55115,7 @@
         <v>0.0154346897202301</v>
       </c>
       <c r="FO113" t="n">
-        <v>523.0815651889894</v>
+        <v>523.0815651889893</v>
       </c>
       <c r="FP113" t="n">
         <v>0</v>
@@ -55124,7 +55124,7 @@
         <v>0</v>
       </c>
       <c r="FR113" t="n">
-        <v>43.73079652570552</v>
+        <v>43.73079652570551</v>
       </c>
       <c r="FS113" t="n">
         <v>0.1784427261739692</v>
@@ -55221,16 +55221,16 @@
         <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>378.0555874319828</v>
+        <v>378.0555874319827</v>
       </c>
       <c r="AA114" t="n">
-        <v>2206.453195243794</v>
+        <v>2206.453195243793</v>
       </c>
       <c r="AB114" t="n">
         <v>0.1713408597322233</v>
       </c>
       <c r="AD114" t="n">
-        <v>330.9679792865691</v>
+        <v>330.967979286569</v>
       </c>
       <c r="AE114" t="n">
         <v>0</v>
@@ -55308,16 +55308,16 @@
         <v>0</v>
       </c>
       <c r="BG114" t="n">
-        <v>422.4441991675668</v>
+        <v>422.4441991675667</v>
       </c>
       <c r="BH114" t="n">
-        <v>2378.575286542524</v>
+        <v>2378.575286542523</v>
       </c>
       <c r="BI114" t="n">
         <v>0.1776038797500616</v>
       </c>
       <c r="BK114" t="n">
-        <v>356.7862929813786</v>
+        <v>356.7862929813785</v>
       </c>
       <c r="BL114" t="n">
         <v>0</v>
@@ -55326,7 +55326,7 @@
         <v>0</v>
       </c>
       <c r="BN114" t="n">
-        <v>36.71257152399167</v>
+        <v>36.71257152399166</v>
       </c>
       <c r="BO114" t="n">
         <v>0.15</v>
@@ -55341,7 +55341,7 @@
         <v>0.01543468972023027</v>
       </c>
       <c r="BT114" t="n">
-        <v>386.2669509476428</v>
+        <v>386.2669509476427</v>
       </c>
       <c r="BU114" t="n">
         <v>0</v>
@@ -55350,7 +55350,7 @@
         <v>0</v>
       </c>
       <c r="BW114" t="n">
-        <v>36.177248219924</v>
+        <v>36.17724821992398</v>
       </c>
       <c r="BX114" t="n">
         <v>0.162394250513347</v>
@@ -55395,16 +55395,16 @@
         <v>0</v>
       </c>
       <c r="CN114" t="n">
-        <v>474.9025575160433</v>
+        <v>474.9025575160432</v>
       </c>
       <c r="CO114" t="n">
-        <v>2576.802126929051</v>
+        <v>2576.80212692905</v>
       </c>
       <c r="CP114" t="n">
         <v>0.184299194941296</v>
       </c>
       <c r="CR114" t="n">
-        <v>386.5203190393576</v>
+        <v>386.5203190393574</v>
       </c>
       <c r="CS114" t="n">
         <v>0</v>
@@ -55413,7 +55413,7 @@
         <v>0</v>
       </c>
       <c r="CU114" t="n">
-        <v>39.77214129957913</v>
+        <v>39.77214129957911</v>
       </c>
       <c r="CV114" t="n">
         <v>0.15</v>
@@ -55428,7 +55428,7 @@
         <v>0.01543468972023019</v>
       </c>
       <c r="DA114" t="n">
-        <v>436.029425266993</v>
+        <v>436.0294252669929</v>
       </c>
       <c r="DB114" t="n">
         <v>0</v>
@@ -55437,7 +55437,7 @@
         <v>0</v>
       </c>
       <c r="DD114" t="n">
-        <v>38.87313224905034</v>
+        <v>38.87313224905032</v>
       </c>
       <c r="DE114" t="n">
         <v>0.1692133907800824</v>
@@ -55482,7 +55482,7 @@
         <v>0</v>
       </c>
       <c r="DU114" t="n">
-        <v>522.4156800250709</v>
+        <v>522.4156800250707</v>
       </c>
       <c r="DV114" t="n">
         <v>2764.430505227906</v>
@@ -55491,7 +55491,7 @@
         <v>0.1889776860142128</v>
       </c>
       <c r="DY114" t="n">
-        <v>414.6645757841859</v>
+        <v>414.6645757841858</v>
       </c>
       <c r="DZ114" t="n">
         <v>0</v>
@@ -55515,7 +55515,7 @@
         <v>0.01543468972023001</v>
       </c>
       <c r="EH114" t="n">
-        <v>480.9512161312134</v>
+        <v>480.9512161312133</v>
       </c>
       <c r="EI114" t="n">
         <v>0</v>
@@ -55524,7 +55524,7 @@
         <v>0</v>
       </c>
       <c r="EK114" t="n">
-        <v>41.46446389385748</v>
+        <v>41.46446389385747</v>
       </c>
       <c r="EL114" t="n">
         <v>0.1739784072059944</v>
@@ -55569,7 +55569,7 @@
         <v>0</v>
       </c>
       <c r="FB114" t="n">
-        <v>573.2053256827833</v>
+        <v>573.205325682783</v>
       </c>
       <c r="FC114" t="n">
         <v>2964.431835003926</v>
@@ -55578,7 +55578,7 @@
         <v>0.193360939831502</v>
       </c>
       <c r="FF114" t="n">
-        <v>444.6647752505889</v>
+        <v>444.6647752505888</v>
       </c>
       <c r="FG114" t="n">
         <v>0</v>
@@ -55602,7 +55602,7 @@
         <v>0.0154346897202301</v>
       </c>
       <c r="FO114" t="n">
-        <v>528.9812981950025</v>
+        <v>528.9812981950024</v>
       </c>
       <c r="FP114" t="n">
         <v>0</v>
@@ -55611,10 +55611,10 @@
         <v>0</v>
       </c>
       <c r="FR114" t="n">
-        <v>44.22402748778069</v>
+        <v>44.22402748778068</v>
       </c>
       <c r="FS114" t="n">
-        <v>0.1784427261739692</v>
+        <v>0.1784427261739691</v>
       </c>
       <c r="FT114" t="n">
         <v>0</v>
@@ -55882,7 +55882,7 @@
         <v>114.633603172815</v>
       </c>
       <c r="CN115" t="n">
-        <v>48.18707263361296</v>
+        <v>48.18707263361297</v>
       </c>
       <c r="CO115" t="n">
         <v>114.633603172815</v>
@@ -55891,7 +55891,7 @@
         <v>0.4203573062339226</v>
       </c>
       <c r="CR115" t="n">
-        <v>43.76585695255058</v>
+        <v>43.76585695255059</v>
       </c>
       <c r="CS115" t="n">
         <v>0</v>
@@ -55915,7 +55915,7 @@
         <v>0</v>
       </c>
       <c r="DA115" t="n">
-        <v>48.18707263361296</v>
+        <v>48.18707263361297</v>
       </c>
       <c r="DB115" t="n">
         <v>0</v>
@@ -57337,16 +57337,16 @@
         <v>4.120085834585201</v>
       </c>
       <c r="CK118" t="n">
-        <v>9861.56193632394</v>
+        <v>9861.561936323942</v>
       </c>
       <c r="CL118" t="n">
-        <v>8217.968280269952</v>
+        <v>8217.968280269954</v>
       </c>
       <c r="CN118" t="n">
         <v>0</v>
       </c>
       <c r="CO118" t="n">
-        <v>8217.968280269952</v>
+        <v>8217.968280269954</v>
       </c>
       <c r="CP118" t="n">
         <v>0</v>
@@ -57824,16 +57824,16 @@
         <v>4.120085834585201</v>
       </c>
       <c r="CK119" t="n">
-        <v>6574.374624215959</v>
+        <v>6574.37462421596</v>
       </c>
       <c r="CL119" t="n">
-        <v>5478.645520179966</v>
+        <v>5478.645520179967</v>
       </c>
       <c r="CN119" t="n">
         <v>0</v>
       </c>
       <c r="CO119" t="n">
-        <v>5478.645520179966</v>
+        <v>5478.645520179967</v>
       </c>
       <c r="CP119" t="n">
         <v>0</v>
@@ -58798,16 +58798,16 @@
         <v>3.533705208630815</v>
       </c>
       <c r="CK121" t="n">
-        <v>4503.317251081604</v>
+        <v>4503.317251081605</v>
       </c>
       <c r="CL121" t="n">
-        <v>3752.764375901337</v>
+        <v>3752.764375901338</v>
       </c>
       <c r="CN121" t="n">
         <v>0</v>
       </c>
       <c r="CO121" t="n">
-        <v>3752.764375901337</v>
+        <v>3752.764375901338</v>
       </c>
       <c r="CP121" t="n">
         <v>0</v>
@@ -59288,13 +59288,13 @@
         <v>329.771115239428</v>
       </c>
       <c r="CL122" t="n">
-        <v>274.8092626995233</v>
+        <v>274.8092626995234</v>
       </c>
       <c r="CN122" t="n">
         <v>0</v>
       </c>
       <c r="CO122" t="n">
-        <v>274.8092626995233</v>
+        <v>274.8092626995234</v>
       </c>
       <c r="CP122" t="n">
         <v>0</v>
@@ -60259,7 +60259,7 @@
         <v>1.994482448766457</v>
       </c>
       <c r="CK124" t="n">
-        <v>127.5926299720513</v>
+        <v>127.5926299720514</v>
       </c>
       <c r="CL124" t="n">
         <v>106.3271916433761</v>
@@ -60746,7 +60746,7 @@
         <v>4.986206121916143</v>
       </c>
       <c r="CK125" t="n">
-        <v>1984.049527001417</v>
+        <v>1984.049527001418</v>
       </c>
       <c r="CL125" t="n">
         <v>1653.374605834514</v>
@@ -61068,7 +61068,7 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>39354.37859118588</v>
+        <v>39354.37859118587</v>
       </c>
       <c r="AB126" t="n">
         <v>0</v>
@@ -61155,7 +61155,7 @@
         <v>0</v>
       </c>
       <c r="BH126" t="n">
-        <v>41147.07851356933</v>
+        <v>41147.07851356932</v>
       </c>
       <c r="BI126" t="n">
         <v>0</v>
@@ -61242,7 +61242,7 @@
         <v>0</v>
       </c>
       <c r="CO126" t="n">
-        <v>43379.14069956581</v>
+        <v>43379.1406995658</v>
       </c>
       <c r="CP126" t="n">
         <v>0</v>
@@ -61329,7 +61329,7 @@
         <v>0</v>
       </c>
       <c r="DV126" t="n">
-        <v>45440.94212802468</v>
+        <v>45440.94212802467</v>
       </c>
       <c r="DW126" t="n">
         <v>0</v>
@@ -61720,16 +61720,16 @@
         <v>10.45337581949606</v>
       </c>
       <c r="CK127" t="n">
-        <v>8247.277712374787</v>
+        <v>8247.277712374789</v>
       </c>
       <c r="CL127" t="n">
-        <v>6872.73142697899</v>
+        <v>6872.731426978991</v>
       </c>
       <c r="CN127" t="n">
         <v>0</v>
       </c>
       <c r="CO127" t="n">
-        <v>6872.73142697899</v>
+        <v>6872.731426978991</v>
       </c>
       <c r="CP127" t="n">
         <v>0</v>
@@ -62207,16 +62207,16 @@
         <v>4.521182288435112</v>
       </c>
       <c r="CK128" t="n">
-        <v>6071.128501471749</v>
+        <v>6071.12850147175</v>
       </c>
       <c r="CL128" t="n">
-        <v>5059.273751226457</v>
+        <v>5059.273751226458</v>
       </c>
       <c r="CN128" t="n">
         <v>0</v>
       </c>
       <c r="CO128" t="n">
-        <v>5059.273751226457</v>
+        <v>5059.273751226458</v>
       </c>
       <c r="CP128" t="n">
         <v>0</v>
@@ -63016,7 +63016,7 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>4140.099204080914</v>
+        <v>4140.099204080913</v>
       </c>
       <c r="AB130" t="n">
         <v>0</v>
@@ -63103,7 +63103,7 @@
         <v>0</v>
       </c>
       <c r="BH130" t="n">
-        <v>4321.460387300458</v>
+        <v>4321.460387300457</v>
       </c>
       <c r="BI130" t="n">
         <v>0</v>
@@ -63190,7 +63190,7 @@
         <v>0</v>
       </c>
       <c r="CO130" t="n">
-        <v>4505.342481497625</v>
+        <v>4505.342481497624</v>
       </c>
       <c r="CP130" t="n">
         <v>0</v>
@@ -63277,7 +63277,7 @@
         <v>0</v>
       </c>
       <c r="DV130" t="n">
-        <v>4692.035905937649</v>
+        <v>4692.035905937648</v>
       </c>
       <c r="DW130" t="n">
         <v>0</v>
@@ -63668,16 +63668,16 @@
         <v>0.03507903262047147</v>
       </c>
       <c r="CK131" t="n">
-        <v>41.75046501907282</v>
+        <v>41.75046501907283</v>
       </c>
       <c r="CL131" t="n">
-        <v>34.79205418256069</v>
+        <v>34.7920541825607</v>
       </c>
       <c r="CN131" t="n">
         <v>0</v>
       </c>
       <c r="CO131" t="n">
-        <v>34.79205418256069</v>
+        <v>34.7920541825607</v>
       </c>
       <c r="CP131" t="n">
         <v>0</v>
@@ -64155,16 +64155,16 @@
         <v>0.07015806524094294</v>
       </c>
       <c r="CK132" t="n">
-        <v>90.76231318829056</v>
+        <v>90.76231318829059</v>
       </c>
       <c r="CL132" t="n">
-        <v>75.63526099024214</v>
+        <v>75.63526099024216</v>
       </c>
       <c r="CN132" t="n">
         <v>0</v>
       </c>
       <c r="CO132" t="n">
-        <v>75.63526099024214</v>
+        <v>75.63526099024216</v>
       </c>
       <c r="CP132" t="n">
         <v>0</v>
@@ -64642,16 +64642,16 @@
         <v>0.3372251715090304</v>
       </c>
       <c r="CK133" t="n">
-        <v>486.7723195963882</v>
+        <v>486.7723195963883</v>
       </c>
       <c r="CL133" t="n">
-        <v>405.6435996636569</v>
+        <v>405.643599663657</v>
       </c>
       <c r="CN133" t="n">
         <v>0</v>
       </c>
       <c r="CO133" t="n">
-        <v>405.6435996636569</v>
+        <v>405.643599663657</v>
       </c>
       <c r="CP133" t="n">
         <v>0</v>
@@ -65451,7 +65451,7 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>22024.94567378788</v>
+        <v>22024.94567378787</v>
       </c>
       <c r="AB135" t="n">
         <v>0</v>
@@ -65625,7 +65625,7 @@
         <v>0</v>
       </c>
       <c r="CO135" t="n">
-        <v>26734.58609421066</v>
+        <v>26734.58609421065</v>
       </c>
       <c r="CP135" t="n">
         <v>0</v>
@@ -66103,16 +66103,16 @@
         <v>0.9188309046089522</v>
       </c>
       <c r="CK136" t="n">
-        <v>6570.547222966367</v>
+        <v>6570.547222966368</v>
       </c>
       <c r="CL136" t="n">
-        <v>5475.45601913864</v>
+        <v>5475.456019138641</v>
       </c>
       <c r="CN136" t="n">
         <v>0</v>
       </c>
       <c r="CO136" t="n">
-        <v>5475.45601913864</v>
+        <v>5475.456019138641</v>
       </c>
       <c r="CP136" t="n">
         <v>0</v>
@@ -66590,7 +66590,7 @@
         <v>0.06479659059758983</v>
       </c>
       <c r="CK137" t="n">
-        <v>78.91401961202054</v>
+        <v>78.91401961202055</v>
       </c>
       <c r="CL137" t="n">
         <v>0</v>
@@ -66894,7 +66894,7 @@
         <v>4966.484111033591</v>
       </c>
       <c r="T138" t="n">
-        <v>0.07305484446442043</v>
+        <v>0.0730548444644204</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -67540,7 +67540,7 @@
         <v>0.03135093789397532</v>
       </c>
       <c r="CC139" t="n">
-        <v>26.58295184130519</v>
+        <v>26.58295184130518</v>
       </c>
       <c r="CD139" t="n">
         <v>6.766569559604957</v>
@@ -67552,7 +67552,7 @@
         <v>4941.294955524905</v>
       </c>
       <c r="CG139" t="n">
-        <v>4215.190125451309</v>
+        <v>4215.190125451308</v>
       </c>
       <c r="CH139" t="n">
         <v>0.142246990155893</v>
@@ -67564,13 +67564,13 @@
         <v>6.624322569449063</v>
       </c>
       <c r="CK139" t="n">
-        <v>4834.207468399421</v>
+        <v>4834.207468399422</v>
       </c>
       <c r="CL139" t="n">
         <v>4123.838744415852</v>
       </c>
       <c r="CN139" t="n">
-        <v>2956.631636151904</v>
+        <v>2956.631636151905</v>
       </c>
       <c r="CO139" t="n">
         <v>4123.838744415852</v>
@@ -67579,7 +67579,7 @@
         <v>0.7169610208826718</v>
       </c>
       <c r="CR139" t="n">
-        <v>2556.780021537828</v>
+        <v>2556.780021537829</v>
       </c>
       <c r="CS139" t="n">
         <v>0</v>
@@ -67588,10 +67588,10 @@
         <v>0</v>
       </c>
       <c r="CU139" t="n">
-        <v>158.5259095097769</v>
+        <v>158.525909509777</v>
       </c>
       <c r="CV139" t="n">
-        <v>0.62</v>
+        <v>0.6200000000000001</v>
       </c>
       <c r="CW139" t="n">
         <v>0</v>
@@ -67612,7 +67612,7 @@
         <v>0</v>
       </c>
       <c r="DD139" t="n">
-        <v>141.5663504524364</v>
+        <v>141.5663504524365</v>
       </c>
       <c r="DE139" t="n">
         <v>0.6826322415034748</v>
@@ -67624,7 +67624,7 @@
         <v>0</v>
       </c>
       <c r="DH139" t="n">
-        <v>0.03432877937919697</v>
+        <v>0.03432877937919698</v>
       </c>
       <c r="DJ139" t="n">
         <v>26.38211932932898</v>
@@ -67639,7 +67639,7 @@
         <v>5111.259239328439</v>
       </c>
       <c r="DN139" t="n">
-        <v>4360.17879283839</v>
+        <v>4360.178792838389</v>
       </c>
       <c r="DO139" t="n">
         <v>0.1411032328095846</v>
@@ -67654,16 +67654,16 @@
         <v>5002.057315073093</v>
       </c>
       <c r="DS139" t="n">
-        <v>4267.023683308499</v>
+        <v>4267.023683308498</v>
       </c>
       <c r="DU139" t="n">
         <v>3149.554825056337</v>
       </c>
       <c r="DV139" t="n">
-        <v>4267.023683308499</v>
+        <v>4267.023683308498</v>
       </c>
       <c r="DW139" t="n">
-        <v>0.7381151497650662</v>
+        <v>0.7381151497650664</v>
       </c>
       <c r="DY139" t="n">
         <v>2645.554683651269</v>
@@ -67678,7 +67678,7 @@
         <v>181.1890393489878</v>
       </c>
       <c r="EC139" t="n">
-        <v>0.6199999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="ED139" t="n">
         <v>0</v>
@@ -67687,7 +67687,7 @@
         <v>0</v>
       </c>
       <c r="EF139" t="n">
-        <v>0.04246262800409399</v>
+        <v>0.042462628004094</v>
       </c>
       <c r="EH139" t="n">
         <v>2992.612043659902</v>
@@ -67702,7 +67702,7 @@
         <v>156.9427813964351</v>
       </c>
       <c r="EL139" t="n">
-        <v>0.7013347630026596</v>
+        <v>0.7013347630026598</v>
       </c>
       <c r="EM139" t="n">
         <v>0</v>
@@ -67711,7 +67711,7 @@
         <v>0</v>
       </c>
       <c r="EO139" t="n">
-        <v>0.03678038676240653</v>
+        <v>0.03678038676240655</v>
       </c>
       <c r="EQ139" t="n">
         <v>26.18529249008507</v>
@@ -67723,7 +67723,7 @@
         <v>0.01365074034144781</v>
       </c>
       <c r="ET139" t="n">
-        <v>5287.57221461881</v>
+        <v>5287.572214618811</v>
       </c>
       <c r="EU139" t="n">
         <v>4510.583235220834</v>
@@ -67744,13 +67744,13 @@
         <v>4416.094663878634</v>
       </c>
       <c r="FB139" t="n">
-        <v>3349.264377906298</v>
+        <v>3349.264377906299</v>
       </c>
       <c r="FC139" t="n">
         <v>4416.094663878634</v>
       </c>
       <c r="FD139" t="n">
-        <v>0.7584222334049007</v>
+        <v>0.7584222334049008</v>
       </c>
       <c r="FF139" t="n">
         <v>2737.978691604753</v>
@@ -67777,7 +67777,7 @@
         <v>0.04643656673189302</v>
       </c>
       <c r="FO139" t="n">
-        <v>3176.246090499967</v>
+        <v>3176.246090499968</v>
       </c>
       <c r="FP139" t="n">
         <v>0</v>
@@ -67786,10 +67786,10 @@
         <v>0</v>
       </c>
       <c r="FR139" t="n">
-        <v>173.0182874063311</v>
+        <v>173.018287406331</v>
       </c>
       <c r="FS139" t="n">
-        <v>0.7192432074611113</v>
+        <v>0.7192432074611114</v>
       </c>
       <c r="FT139" t="n">
         <v>0</v>
@@ -67798,7 +67798,7 @@
         <v>0</v>
       </c>
       <c r="FV139" t="n">
-        <v>0.03917902594378943</v>
+        <v>0.03917902594378942</v>
       </c>
     </row>
     <row r="140">
@@ -68051,16 +68051,16 @@
         <v>13.78246356913428</v>
       </c>
       <c r="CK140" t="n">
-        <v>691.4700099874067</v>
+        <v>691.4700099874068</v>
       </c>
       <c r="CL140" t="n">
-        <v>576.2250083228389</v>
+        <v>576.225008322839</v>
       </c>
       <c r="CN140" t="n">
         <v>0</v>
       </c>
       <c r="CO140" t="n">
-        <v>576.2250083228389</v>
+        <v>576.225008322839</v>
       </c>
       <c r="CP140" t="n">
         <v>0</v>
@@ -68842,28 +68842,28 @@
         <v>4285.562967795609</v>
       </c>
       <c r="T142" t="n">
-        <v>0.5151266437792513</v>
+        <v>0.5151266437792512</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
       </c>
       <c r="V142" t="n">
-        <v>5.575154888193848</v>
+        <v>5.575154888193849</v>
       </c>
       <c r="W142" t="n">
-        <v>4634.705504774221</v>
+        <v>4634.705504774222</v>
       </c>
       <c r="X142" t="n">
-        <v>3923.323856905024</v>
+        <v>3923.323856905025</v>
       </c>
       <c r="Z142" t="n">
         <v>2728.832930377668</v>
       </c>
       <c r="AA142" t="n">
-        <v>3923.323856905024</v>
+        <v>3923.323856905025</v>
       </c>
       <c r="AB142" t="n">
-        <v>0.6955410845258007</v>
+        <v>0.6955410845258008</v>
       </c>
       <c r="AD142" t="n">
         <v>2638.435293768629</v>
@@ -68902,7 +68902,7 @@
         <v>0</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.6955410845258007</v>
+        <v>0.6955410845258008</v>
       </c>
       <c r="AR142" t="n">
         <v>0</v>
@@ -69016,7 +69016,7 @@
         <v>4529.392543328731</v>
       </c>
       <c r="CH142" t="n">
-        <v>0.5152693984755998</v>
+        <v>0.5152693984755999</v>
       </c>
       <c r="CI142" t="n">
         <v>0</v>
@@ -69025,13 +69025,13 @@
         <v>5.623798613470105</v>
       </c>
       <c r="CK142" t="n">
-        <v>4898.316530537521</v>
+        <v>4898.316530537522</v>
       </c>
       <c r="CL142" t="n">
         <v>4146.473186512912</v>
       </c>
       <c r="CN142" t="n">
-        <v>3070.197100153488</v>
+        <v>3070.197100153489</v>
       </c>
       <c r="CO142" t="n">
         <v>4146.473186512912</v>
@@ -69040,7 +69040,7 @@
         <v>0.7404357780823981</v>
       </c>
       <c r="CR142" t="n">
-        <v>2788.503217929933</v>
+        <v>2788.503217929934</v>
       </c>
       <c r="CS142" t="n">
         <v>0</v>
@@ -69064,7 +69064,7 @@
         <v>0</v>
       </c>
       <c r="DA142" t="n">
-        <v>3070.197100153488</v>
+        <v>3070.197100153489</v>
       </c>
       <c r="DB142" t="n">
         <v>0</v>
@@ -69190,7 +69190,7 @@
         <v>4695.86721623319</v>
       </c>
       <c r="EV142" t="n">
-        <v>0.5133534489454814</v>
+        <v>0.5133534489454815</v>
       </c>
       <c r="EW142" t="n">
         <v>0</v>
@@ -69205,13 +69205,13 @@
         <v>4302.675473610897</v>
       </c>
       <c r="FB142" t="n">
-        <v>3356.718786829913</v>
+        <v>3356.718786829914</v>
       </c>
       <c r="FC142" t="n">
         <v>4302.675473610897</v>
       </c>
       <c r="FD142" t="n">
-        <v>0.7801468661574151</v>
+        <v>0.7801468661574152</v>
       </c>
       <c r="FF142" t="n">
         <v>2893.549256003329</v>
@@ -69238,7 +69238,7 @@
         <v>0</v>
       </c>
       <c r="FO142" t="n">
-        <v>3356.718786829913</v>
+        <v>3356.718786829914</v>
       </c>
       <c r="FP142" t="n">
         <v>0</v>
@@ -69250,7 +69250,7 @@
         <v>0</v>
       </c>
       <c r="FS142" t="n">
-        <v>0.7801468661574151</v>
+        <v>0.7801468661574152</v>
       </c>
       <c r="FT142" t="n">
         <v>0</v>
@@ -69512,22 +69512,22 @@
         <v>3.069534005972853</v>
       </c>
       <c r="CK143" t="n">
-        <v>4753.798180490776</v>
+        <v>4753.798180490777</v>
       </c>
       <c r="CL143" t="n">
-        <v>4028.730430518835</v>
+        <v>4028.730430518836</v>
       </c>
       <c r="CN143" t="n">
         <v>2983.016151005448</v>
       </c>
       <c r="CO143" t="n">
-        <v>4028.730430518835</v>
+        <v>4028.730430518836</v>
       </c>
       <c r="CP143" t="n">
-        <v>0.740435778082398</v>
+        <v>0.7404357780823977</v>
       </c>
       <c r="CR143" t="n">
-        <v>2709.321214523916</v>
+        <v>2709.321214523917</v>
       </c>
       <c r="CS143" t="n">
         <v>0</v>
@@ -69563,7 +69563,7 @@
         <v>0</v>
       </c>
       <c r="DE143" t="n">
-        <v>0.740435778082398</v>
+        <v>0.7404357780823977</v>
       </c>
       <c r="DF143" t="n">
         <v>0</v>
@@ -69698,7 +69698,7 @@
         <v>4240.334481148639</v>
       </c>
       <c r="FD143" t="n">
-        <v>0.7801468661574152</v>
+        <v>0.7801468661574154</v>
       </c>
       <c r="FF143" t="n">
         <v>2851.624938572461</v>
@@ -69737,7 +69737,7 @@
         <v>0</v>
       </c>
       <c r="FS143" t="n">
-        <v>0.7801468661574152</v>
+        <v>0.7801468661574154</v>
       </c>
       <c r="FT143" t="n">
         <v>0</v>
@@ -69999,16 +69999,16 @@
         <v>1.169301087349049</v>
       </c>
       <c r="CK144" t="n">
-        <v>463.5465285766538</v>
+        <v>463.5465285766539</v>
       </c>
       <c r="CL144" t="n">
-        <v>386.2887738138781</v>
+        <v>386.2887738138782</v>
       </c>
       <c r="CN144" t="n">
         <v>0</v>
       </c>
       <c r="CO144" t="n">
-        <v>386.2887738138781</v>
+        <v>386.2887738138782</v>
       </c>
       <c r="CP144" t="n">
         <v>0</v>
@@ -70486,16 +70486,16 @@
         <v>4.677204349396196</v>
       </c>
       <c r="CK145" t="n">
-        <v>4966.671990943091</v>
+        <v>4966.671990943092</v>
       </c>
       <c r="CL145" t="n">
-        <v>4138.89332578591</v>
+        <v>4138.893325785911</v>
       </c>
       <c r="CN145" t="n">
         <v>0</v>
       </c>
       <c r="CO145" t="n">
-        <v>4138.89332578591</v>
+        <v>4138.893325785911</v>
       </c>
       <c r="CP145" t="n">
         <v>0</v>
@@ -70790,7 +70790,7 @@
         <v>1161.525460351862</v>
       </c>
       <c r="T146" t="n">
-        <v>0.0005521688058480778</v>
+        <v>0.0005521688058480777</v>
       </c>
       <c r="U146" t="n">
         <v>0</v>
@@ -70964,7 +70964,7 @@
         <v>1326.838299466124</v>
       </c>
       <c r="CH146" t="n">
-        <v>0.000602239672787767</v>
+        <v>0.0006022396727877671</v>
       </c>
       <c r="CI146" t="n">
         <v>0</v>
@@ -70973,22 +70973,22 @@
         <v>1.214706899068097</v>
       </c>
       <c r="CK146" t="n">
-        <v>1583.925292700178</v>
+        <v>1583.925292700179</v>
       </c>
       <c r="CL146" t="n">
-        <v>1325.300367648747</v>
+        <v>1325.300367648748</v>
       </c>
       <c r="CN146" t="n">
-        <v>408.5709241570391</v>
+        <v>408.5709241570392</v>
       </c>
       <c r="CO146" t="n">
-        <v>1325.300367648747</v>
+        <v>1325.300367648748</v>
       </c>
       <c r="CP146" t="n">
         <v>0.3082855284209241</v>
       </c>
       <c r="CR146" t="n">
-        <v>371.0841029416493</v>
+        <v>371.0841029416495</v>
       </c>
       <c r="CS146" t="n">
         <v>0</v>
@@ -71012,7 +71012,7 @@
         <v>0</v>
       </c>
       <c r="DA146" t="n">
-        <v>408.5709241570391</v>
+        <v>408.5709241570392</v>
       </c>
       <c r="DB146" t="n">
         <v>0</v>
@@ -71138,7 +71138,7 @@
         <v>1534.479909595831</v>
       </c>
       <c r="EV146" t="n">
-        <v>0.0006608192135309864</v>
+        <v>0.0006608192135309866</v>
       </c>
       <c r="EW146" t="n">
         <v>0</v>
@@ -71153,13 +71153,13 @@
         <v>1533.768931500096</v>
       </c>
       <c r="FB146" t="n">
-        <v>498.1980774564072</v>
+        <v>498.1980774564074</v>
       </c>
       <c r="FC146" t="n">
         <v>1533.768931500096</v>
       </c>
       <c r="FD146" t="n">
-        <v>0.3248195130469535</v>
+        <v>0.3248195130469536</v>
       </c>
       <c r="FF146" t="n">
         <v>429.4553008200268</v>
@@ -71186,7 +71186,7 @@
         <v>0</v>
       </c>
       <c r="FO146" t="n">
-        <v>498.1980774564072</v>
+        <v>498.1980774564074</v>
       </c>
       <c r="FP146" t="n">
         <v>0</v>
@@ -71198,7 +71198,7 @@
         <v>0</v>
       </c>
       <c r="FS146" t="n">
-        <v>0.3248195130469535</v>
+        <v>0.3248195130469536</v>
       </c>
       <c r="FT146" t="n">
         <v>0</v>
@@ -71463,13 +71463,13 @@
         <v>2062.75464697783</v>
       </c>
       <c r="CL147" t="n">
-        <v>1718.962205814858</v>
+        <v>1718.962205814859</v>
       </c>
       <c r="CN147" t="n">
         <v>0</v>
       </c>
       <c r="CO147" t="n">
-        <v>1718.962205814858</v>
+        <v>1718.962205814859</v>
       </c>
       <c r="CP147" t="n">
         <v>0</v>
@@ -72437,13 +72437,13 @@
         <v>14663.56099005086</v>
       </c>
       <c r="CL149" t="n">
-        <v>12219.63415837571</v>
+        <v>12219.63415837572</v>
       </c>
       <c r="CN149" t="n">
         <v>0</v>
       </c>
       <c r="CO149" t="n">
-        <v>12219.63415837571</v>
+        <v>12219.63415837572</v>
       </c>
       <c r="CP149" t="n">
         <v>0</v>
@@ -72921,16 +72921,16 @@
         <v>2.772681472175708</v>
       </c>
       <c r="CK150" t="n">
-        <v>7184.716563507951</v>
+        <v>7184.716563507953</v>
       </c>
       <c r="CL150" t="n">
-        <v>5987.263802923292</v>
+        <v>5987.263802923294</v>
       </c>
       <c r="CN150" t="n">
         <v>0</v>
       </c>
       <c r="CO150" t="n">
-        <v>5987.263802923292</v>
+        <v>5987.263802923294</v>
       </c>
       <c r="CP150" t="n">
         <v>0</v>
@@ -73408,16 +73408,16 @@
         <v>3.864607113365085</v>
       </c>
       <c r="CK151" t="n">
-        <v>4772.795370394681</v>
+        <v>4772.795370394682</v>
       </c>
       <c r="CL151" t="n">
-        <v>3977.329475328901</v>
+        <v>3977.329475328902</v>
       </c>
       <c r="CN151" t="n">
         <v>0</v>
       </c>
       <c r="CO151" t="n">
-        <v>3977.329475328901</v>
+        <v>3977.329475328902</v>
       </c>
       <c r="CP151" t="n">
         <v>0</v>
@@ -73895,16 +73895,16 @@
         <v>0.7819573745567837</v>
       </c>
       <c r="CK152" t="n">
-        <v>810.0172753556222</v>
+        <v>810.0172753556224</v>
       </c>
       <c r="CL152" t="n">
-        <v>675.0143961296853</v>
+        <v>675.0143961296855</v>
       </c>
       <c r="CN152" t="n">
         <v>0</v>
       </c>
       <c r="CO152" t="n">
-        <v>675.0143961296853</v>
+        <v>675.0143961296855</v>
       </c>
       <c r="CP152" t="n">
         <v>0</v>
@@ -74391,7 +74391,7 @@
         <v>0</v>
       </c>
       <c r="CO153" t="n">
-        <v>153.6718015805453</v>
+        <v>153.6718015805454</v>
       </c>
       <c r="CP153" t="n">
         <v>0</v>
